--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -828,37 +828,6 @@
   </si>
   <si>
     <t>The categorization is often highly contextual and may appear poorly differentiated or not very useful in other contexts.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>&lt; 404684003 |Clinical finding|</t>
-  </si>
-  <si>
-    <t>'problem' if from PRB-3. 'diagnosis' if from DG1 segment in PV1 message</t>
-  </si>
-  <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>1608: fixed value = http://terminology.hl7.org/CodeSystem/condition-category|encounter-diagnosis</t>
-  </si>
-  <si>
-    <t>Condition.category:us-core</t>
-  </si>
-  <si>
-    <t>us-core</t>
-  </si>
-  <si>
-    <t>encounter-diagnosis</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -867,6 +836,37 @@
     &lt;code value="encounter-diagnosis"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/condition-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>&lt; 404684003 |Clinical finding|</t>
+  </si>
+  <si>
+    <t>'problem' if from PRB-3. 'diagnosis' if from DG1 segment in PV1 message</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>1608: fixed value = http://terminology.hl7.org/CodeSystem/condition-category#encounter-diagnosis</t>
+  </si>
+  <si>
+    <t>Condition.category:us-core</t>
+  </si>
+  <si>
+    <t>us-core</t>
+  </si>
+  <si>
+    <t>encounter-diagnosis</t>
   </si>
   <si>
     <t>Condition.severity</t>
@@ -4558,7 +4558,7 @@
         <v>81</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>81</v>
+        <v>261</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>81</v>
@@ -4579,13 +4579,13 @@
         <v>259</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -4613,22 +4613,22 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>81</v>
@@ -4636,13 +4636,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>257</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>81</v>
@@ -4667,7 +4667,7 @@
         <v>190</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M24" t="s" s="2">
         <v>259</v>
@@ -4684,7 +4684,7 @@
         <v>81</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>81</v>
@@ -4705,7 +4705,7 @@
         <v>259</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>81</v>
@@ -4741,16 +4741,16 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>81</v>
@@ -7623,7 +7623,7 @@
         <v>415</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="430">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -778,8 +778,7 @@
     <t>604: terminologyMaps using VF_encounterProblemStatus on V POV - MODIFIER (#9000010.07-.06)</t>
   </si>
   <si>
-    <t>Outpat.VDiagnosis.Modifier
-Outpat.WorkloadVDiagnosis.Modifier</t>
+    <t>Outpat.VDiagnosis.Modifier,Outpat.WorkloadVDiagnosis.Modifier</t>
   </si>
   <si>
     <t>Condition.verificationStatus</t>
@@ -1047,8 +1046,7 @@
     <t>368: source value from V POV - VISIT (#9000010.07-.03)</t>
   </si>
   <si>
-    <t>Outpat.VDiagnosis.VisitDateTime
-Outpat.WorkloadVDiagnosis.VisitDateTime</t>
+    <t>Outpat.VDiagnosis.VisitDateTime,Outpat.WorkloadVDiagnosis.VisitDateTime</t>
   </si>
   <si>
     <t>Condition.onset[x]</t>
@@ -1096,8 +1094,7 @@
     <t>370: source value from V POV - DATE OF INJURY (#9000010.07-.13)</t>
   </si>
   <si>
-    <t>Outpat.VDiagnosis.InjuryDateTime
-Outpat.WorkloadVDiagnosis.InjuryDateTime</t>
+    <t>Outpat.VDiagnosis.InjuryDateTime,Outpat.WorkloadVDiagnosis.InjuryDateTime</t>
   </si>
   <si>
     <t>Condition.abatement[x]</t>
@@ -1141,6 +1138,10 @@
   </si>
   <si>
     <t>372: source value from V POV - VISIT &gt; VISIT - VISIT/ADMIT DATE&amp;TIME (#9000010.07-.03 &gt; 9000010-.01)</t>
+  </si>
+  <si>
+    <t>Outpat.VDiagnosis.VisitDateTime,Outpat.WorkloadVDiagnosis.VisitDateTime
+Outpat.Visit.VisitDateTime,Outpat.Workload.VisitDateTime</t>
   </si>
   <si>
     <t>Condition.recorder</t>
@@ -1729,7 +1730,7 @@
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
     <col min="43" max="43" width="102.29296875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="73.890625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5891,15 +5892,15 @@
         <v>356</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>327</v>
+        <v>357</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5922,13 +5923,13 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5979,7 +5980,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6003,10 +6004,10 @@
         <v>81</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>81</v>
@@ -6020,10 +6021,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6046,13 +6047,13 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6103,7 +6104,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6124,13 +6125,13 @@
         <v>81</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>81</v>
@@ -6144,10 +6145,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6170,13 +6171,13 @@
         <v>81</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6227,7 +6228,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6239,7 +6240,7 @@
         <v>81</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>81</v>
@@ -6251,7 +6252,7 @@
         <v>81</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>81</v>
@@ -6268,10 +6269,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6392,10 +6393,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6518,14 +6519,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6547,10 +6548,10 @@
         <v>138</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>156</v>
@@ -6605,7 +6606,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6646,10 +6647,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6675,10 +6676,10 @@
         <v>190</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6708,10 +6709,10 @@
         <v>300</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
@@ -6729,7 +6730,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -6738,7 +6739,7 @@
         <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>105</v>
@@ -6747,7 +6748,7 @@
         <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>241</v>
@@ -6770,10 +6771,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6796,13 +6797,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6853,7 +6854,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -6862,7 +6863,7 @@
         <v>83</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>105</v>
@@ -6877,7 +6878,7 @@
         <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>81</v>
@@ -6894,10 +6895,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6923,10 +6924,10 @@
         <v>190</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6956,10 +6957,10 @@
         <v>300</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>81</v>
@@ -6977,7 +6978,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7001,7 +7002,7 @@
         <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>81</v>
@@ -7018,10 +7019,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7044,16 +7045,16 @@
         <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7103,7 +7104,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7115,7 +7116,7 @@
         <v>81</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>81</v>
@@ -7127,7 +7128,7 @@
         <v>81</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>81</v>
@@ -7144,10 +7145,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7268,10 +7269,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7394,14 +7395,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7423,10 +7424,10 @@
         <v>138</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>156</v>
@@ -7481,7 +7482,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7522,10 +7523,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7551,10 +7552,10 @@
         <v>190</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7584,10 +7585,10 @@
         <v>300</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>81</v>
@@ -7605,7 +7606,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7614,13 +7615,13 @@
         <v>83</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>264</v>
@@ -7629,10 +7630,10 @@
         <v>81</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>81</v>
@@ -7646,10 +7647,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7672,13 +7673,13 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7729,7 +7730,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -7738,7 +7739,7 @@
         <v>83</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>105</v>
@@ -7753,10 +7754,10 @@
         <v>81</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>81</v>
@@ -7770,10 +7771,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7796,13 +7797,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7853,7 +7854,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -7868,16 +7869,16 @@
         <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -253,12 +259,6 @@
   </si>
   <si>
     <t>Mapping: SNOMED CT Attribute Binding</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t/>
@@ -684,13 +684,13 @@
     <t>Identifier.value</t>
   </si>
   <si>
+    <t>346: source value from V POV - IEN (#9000010.07-.001)</t>
+  </si>
+  <si>
     <t>CX.1 / EI.1</t>
   </si>
   <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>346: source value from V POV - IEN (#9000010.07-.001)</t>
   </si>
   <si>
     <t>Condition.identifier.period</t>
@@ -759,6 +759,12 @@
 con-4con-5</t>
   </si>
   <si>
+    <t>604: terminologyMaps using VF_encounterProblemStatus on V POV - MODIFIER (#9000010.07-.06)</t>
+  </si>
+  <si>
+    <t>Outpat.VDiagnosis.Modifier,Outpat.WorkloadVDiagnosis.Modifier</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -775,12 +781,6 @@
     <t>FiveWs.status</t>
   </si>
   <si>
-    <t>604: terminologyMaps using VF_encounterProblemStatus on V POV - MODIFIER (#9000010.07-.06)</t>
-  </si>
-  <si>
-    <t>Outpat.VDiagnosis.Modifier,Outpat.WorkloadVDiagnosis.Modifier</t>
-  </si>
-  <si>
     <t>Condition.verificationStatus</t>
   </si>
   <si>
@@ -801,6 +801,9 @@
 con-5</t>
   </si>
   <si>
+    <t>606: terminologyMaps using VF_encounterProblemVerificationStatus on V POV - MODIFIER (#9000010.07-.06)</t>
+  </si>
+  <si>
     <t>&lt; 410514004 |Finding context value|</t>
   </si>
   <si>
@@ -814,9 +817,6 @@
     <t>408729009</t>
   </si>
   <si>
-    <t>606: terminologyMaps using VF_encounterProblemVerificationStatus on V POV - MODIFIER (#9000010.07-.06)</t>
-  </si>
-  <si>
     <t>Condition.category</t>
   </si>
   <si>
@@ -827,6 +827,34 @@
   </si>
   <si>
     <t>The categorization is often highly contextual and may appear poorly differentiated or not very useful in other contexts.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/condition-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>&lt; 404684003 |Clinical finding|</t>
+  </si>
+  <si>
+    <t>'problem' if from PRB-3. 'diagnosis' if from DG1 segment in PV1 message</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Condition.category:us-core</t>
+  </si>
+  <si>
+    <t>us-core</t>
+  </si>
+  <si>
+    <t>encounter-diagnosis</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -837,35 +865,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>&lt; 404684003 |Clinical finding|</t>
-  </si>
-  <si>
-    <t>'problem' if from PRB-3. 'diagnosis' if from DG1 segment in PV1 message</t>
-  </si>
-  <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
     <t>1608: fixed value = http://terminology.hl7.org/CodeSystem/condition-category#encounter-diagnosis</t>
-  </si>
-  <si>
-    <t>Condition.category:us-core</t>
-  </si>
-  <si>
-    <t>us-core</t>
-  </si>
-  <si>
-    <t>encounter-diagnosis</t>
   </si>
   <si>
     <t>Condition.severity</t>
@@ -918,6 +918,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-condition-code</t>
+  </si>
+  <si>
+    <t>1613: source value from V POV - POV &gt; ICD DIAGNOSIS (#9000010.07-.01 &gt; 80-)</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -947,9 +950,6 @@
     <t>246090004</t>
   </si>
   <si>
-    <t>1613: source value from V POV - POV &gt; ICD DIAGNOSIS (#9000010.07-.01 &gt; 80-)</t>
-  </si>
-  <si>
     <t>Condition.bodySite</t>
   </si>
   <si>
@@ -1000,6 +1000,9 @@
     <t>Group is typically used for veterinary or public health use cases.</t>
   </si>
   <si>
+    <t>1611: reference from V POV - PATIENT NAME (#9000010.07-.02)</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -1010,9 +1013,6 @@
   </si>
   <si>
     <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>1611: reference from V POV - PATIENT NAME (#9000010.07-.02)</t>
   </si>
   <si>
     <t>Condition.encounter</t>
@@ -1031,6 +1031,12 @@
     <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter. This record indicates the encounter this particular record is associated with.  In the case of a "new" diagnosis reflecting ongoing/revised information about the condition, this might be distinct from the first encounter in which the underlying condition was first "known".</t>
   </si>
   <si>
+    <t>368: source value from V POV - VISIT (#9000010.07-.03)</t>
+  </si>
+  <si>
+    <t>Outpat.VDiagnosis.VisitDateTime,Outpat.WorkloadVDiagnosis.VisitDateTime</t>
+  </si>
+  <si>
     <t>Event.context</t>
   </si>
   <si>
@@ -1041,12 +1047,6 @@
   </si>
   <si>
     <t>FiveWs.context</t>
-  </si>
-  <si>
-    <t>368: source value from V POV - VISIT (#9000010.07-.03)</t>
-  </si>
-  <si>
-    <t>Outpat.VDiagnosis.VisitDateTime,Outpat.WorkloadVDiagnosis.VisitDateTime</t>
   </si>
   <si>
     <t>Condition.onset[x]</t>
@@ -1128,20 +1128,20 @@
     <t>The recordedDate represents when this particular Condition record was created in the system, which is often a system-generated date.</t>
   </si>
   <si>
-    <t>REL-11</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=AUT].time</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
     <t>372: source value from V POV - VISIT &gt; VISIT - VISIT/ADMIT DATE&amp;TIME (#9000010.07-.03 &gt; 9000010-.01)</t>
   </si>
   <si>
     <t>Outpat.VDiagnosis.VisitDateTime,Outpat.WorkloadVDiagnosis.VisitDateTime
 Outpat.Visit.VisitDateTime,Outpat.Workload.VisitDateTime</t>
+  </si>
+  <si>
+    <t>REL-11</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=AUT].time</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
   </si>
   <si>
     <t>Condition.recorder</t>
@@ -1723,14 +1723,14 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="68.20703125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="222.1015625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="102.29296875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="73.890625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="102.29296875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="73.890625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="68.20703125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="222.1015625" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1969,22 +1969,22 @@
         <v>87</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AN2" t="s" s="2">
+      <c r="AP2" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP2" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ2" t="s" s="2">
         <v>81</v>
@@ -2606,13 +2606,13 @@
         <v>81</v>
       </c>
       <c r="AN7" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP7" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP7" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ7" t="s" s="2">
         <v>81</v>
@@ -2732,13 +2732,13 @@
         <v>81</v>
       </c>
       <c r="AN8" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO8" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP8" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP8" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ8" t="s" s="2">
         <v>81</v>
@@ -3110,13 +3110,13 @@
         <v>81</v>
       </c>
       <c r="AN11" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO11" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP11" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ11" t="s" s="2">
         <v>81</v>
@@ -3229,25 +3229,25 @@
         <v>105</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="AL12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AN12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP12" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AO12" t="s" s="2">
+      <c r="AQ12" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ12" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR12" t="s" s="2">
         <v>81</v>
@@ -3362,13 +3362,13 @@
         <v>81</v>
       </c>
       <c r="AN13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP13" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP13" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ13" t="s" s="2">
         <v>81</v>
@@ -3488,13 +3488,13 @@
         <v>81</v>
       </c>
       <c r="AN14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP14" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP14" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ14" t="s" s="2">
         <v>81</v>
@@ -3613,16 +3613,16 @@
         <v>81</v>
       </c>
       <c r="AM15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="AN15" t="s" s="2">
+      <c r="AP15" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>81</v>
@@ -3741,16 +3741,16 @@
         <v>81</v>
       </c>
       <c r="AM16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AP16" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>81</v>
@@ -3869,16 +3869,16 @@
         <v>81</v>
       </c>
       <c r="AM17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>81</v>
@@ -3989,25 +3989,25 @@
         <v>105</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>81</v>
+        <v>215</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>215</v>
+        <v>81</v>
       </c>
       <c r="AN18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AO18" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AP18" t="s" s="2">
-        <v>81</v>
+        <v>217</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>217</v>
+        <v>81</v>
       </c>
       <c r="AR18" t="s" s="2">
         <v>81</v>
@@ -4119,16 +4119,16 @@
         <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AP19" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>81</v>
@@ -4245,16 +4245,16 @@
         <v>81</v>
       </c>
       <c r="AM20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>81</v>
@@ -4378,13 +4378,13 @@
         <v>243</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>81</v>
+        <v>244</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>245</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" hidden="true">
@@ -4487,28 +4487,28 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>255</v>
       </c>
       <c r="AQ22" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AR22" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AR22" t="s" s="2">
-        <v>245</v>
       </c>
     </row>
     <row r="23" hidden="true">
@@ -4559,7 +4559,7 @@
         <v>81</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>261</v>
+        <v>81</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>81</v>
@@ -4580,13 +4580,13 @@
         <v>259</v>
       </c>
       <c r="Z23" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB23" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -4614,22 +4614,22 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AP23" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AQ23" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>81</v>
@@ -4637,13 +4637,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>257</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>81</v>
@@ -4668,7 +4668,7 @@
         <v>190</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M24" t="s" s="2">
         <v>259</v>
@@ -4685,7 +4685,7 @@
         <v>81</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>81</v>
@@ -4706,7 +4706,7 @@
         <v>259</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>81</v>
@@ -4739,25 +4739,25 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>81</v>
+        <v>271</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AQ24" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>81</v>
@@ -4868,25 +4868,25 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AO25" t="s" s="2">
+      <c r="AQ25" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AP25" t="s" s="2">
+      <c r="AR25" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR25" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="26" hidden="true">
@@ -4994,25 +4994,25 @@
         <v>289</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AO26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AP26" t="s" s="2">
+      <c r="AQ26" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AQ26" t="s" s="2">
+      <c r="AR26" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AR26" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="27" hidden="true">
@@ -5120,25 +5120,25 @@
         <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP27" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AO27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP27" t="s" s="2">
+      <c r="AQ27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR27" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AQ27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR27" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="28" hidden="true">
@@ -5252,13 +5252,13 @@
         <v>313</v>
       </c>
       <c r="AN28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="AO28" t="s" s="2">
+      <c r="AP28" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>316</v>
@@ -5372,25 +5372,25 @@
         <v>322</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>81</v>
+        <v>323</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>325</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>81</v>
+        <v>326</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>327</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" hidden="true">
@@ -5493,25 +5493,25 @@
         <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AL30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AP30" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AO30" t="s" s="2">
+      <c r="AQ30" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>81</v>
@@ -5621,28 +5621,28 @@
         <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AL31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AP31" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AO31" t="s" s="2">
+      <c r="AQ31" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AP31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ31" t="s" s="2">
-        <v>341</v>
-      </c>
       <c r="AR31" t="s" s="2">
-        <v>342</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" hidden="true">
@@ -5756,16 +5756,16 @@
         <v>81</v>
       </c>
       <c r="AN32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP32" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AO32" t="s" s="2">
+      <c r="AQ32" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ32" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>81</v>
@@ -5871,28 +5871,28 @@
         <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>81</v>
+        <v>353</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>81</v>
+        <v>354</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>353</v>
+        <v>81</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>354</v>
+        <v>81</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>355</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>81</v>
+        <v>356</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>357</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" hidden="true">
@@ -6004,16 +6004,16 @@
         <v>81</v>
       </c>
       <c r="AN34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP34" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="AO34" t="s" s="2">
+      <c r="AQ34" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ34" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>81</v>
@@ -6125,19 +6125,19 @@
         <v>81</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AP35" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AO35" t="s" s="2">
+      <c r="AQ35" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ35" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>81</v>
@@ -6252,13 +6252,13 @@
         <v>81</v>
       </c>
       <c r="AN36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP36" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>81</v>
@@ -6376,13 +6376,13 @@
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>81</v>
@@ -6502,13 +6502,13 @@
         <v>81</v>
       </c>
       <c r="AN38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP38" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>81</v>
@@ -6630,13 +6630,13 @@
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP39" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>81</v>
@@ -6748,19 +6748,19 @@
         <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AM40" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AO40" t="s" s="2">
-        <v>81</v>
+        <v>243</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>81</v>
+        <v>293</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>81</v>
@@ -6878,13 +6878,13 @@
         <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP41" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>81</v>
@@ -7002,13 +7002,13 @@
         <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP42" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>81</v>
@@ -7128,13 +7128,13 @@
         <v>81</v>
       </c>
       <c r="AN43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP43" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>81</v>
@@ -7252,13 +7252,13 @@
         <v>81</v>
       </c>
       <c r="AN44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP44" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>81</v>
@@ -7378,13 +7378,13 @@
         <v>81</v>
       </c>
       <c r="AN45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP45" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>81</v>
@@ -7506,13 +7506,13 @@
         <v>81</v>
       </c>
       <c r="AN46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>81</v>
@@ -7621,25 +7621,25 @@
         <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AL47" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AN47" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AO47" t="s" s="2">
+      <c r="AQ47" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>81</v>
@@ -7754,16 +7754,16 @@
         <v>81</v>
       </c>
       <c r="AN48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP48" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="AO48" t="s" s="2">
+      <c r="AQ48" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ48" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>81</v>
@@ -7869,22 +7869,22 @@
         <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AL49" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AP49" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$50</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2030" uniqueCount="433">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1117,6 +1117,15 @@
   </si>
   <si>
     <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementDateTime</t>
+  </si>
+  <si>
+    <t>abatementDateTime</t>
+  </si>
+  <si>
+    <t>1766: target not supported</t>
   </si>
   <si>
     <t>Condition.recordedDate</t>
@@ -1685,12 +1694,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR49"/>
+  <dimension ref="A1:AR50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="35.88671875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.5390625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="35.88671875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.0546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="20.01953125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -5720,16 +5729,14 @@
         <v>81</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="AC32" s="2"/>
       <c r="AD32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>343</v>
@@ -5776,9 +5783,11 @@
         <v>350</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="C33" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="D33" t="s" s="2">
         <v>81</v>
       </c>
@@ -5796,18 +5805,20 @@
         <v>81</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
         <v>340</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>346</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>81</v>
@@ -5856,7 +5867,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -5865,16 +5876,16 @@
         <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>81</v>
+        <v>347</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>354</v>
+        <v>81</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>81</v>
@@ -5883,13 +5894,13 @@
         <v>81</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>355</v>
+        <v>81</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>81</v>
@@ -5897,10 +5908,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5914,7 +5925,7 @@
         <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>81</v>
@@ -5923,13 +5934,13 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5980,7 +5991,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -5995,10 +6006,10 @@
         <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>81</v>
+        <v>356</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>81</v>
+        <v>357</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>81</v>
@@ -6007,13 +6018,13 @@
         <v>81</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>81</v>
+        <v>358</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>81</v>
@@ -6021,10 +6032,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6047,13 +6058,13 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6104,7 +6115,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6131,13 +6142,13 @@
         <v>81</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>367</v>
+        <v>81</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>81</v>
@@ -6145,10 +6156,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6159,7 +6170,7 @@
         <v>82</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>81</v>
@@ -6168,16 +6179,16 @@
         <v>81</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6228,40 +6239,40 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AG36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AP36" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>81</v>
+        <v>372</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>81</v>
@@ -6269,10 +6280,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6283,7 +6294,7 @@
         <v>82</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>81</v>
@@ -6295,13 +6306,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>169</v>
+        <v>374</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>170</v>
+        <v>375</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>171</v>
+        <v>376</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6352,19 +6363,19 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>172</v>
+        <v>373</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>81</v>
+        <v>377</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>81</v>
@@ -6382,7 +6393,7 @@
         <v>81</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>173</v>
+        <v>378</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>81</v>
@@ -6393,21 +6404,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>81</v>
@@ -6419,17 +6430,15 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>81</v>
@@ -6478,19 +6487,19 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>144</v>
+        <v>81</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>81</v>
@@ -6519,14 +6528,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>379</v>
+        <v>153</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6539,26 +6548,24 @@
         <v>81</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
         <v>138</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>380</v>
+        <v>175</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>381</v>
+        <v>176</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="O39" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>81</v>
       </c>
@@ -6606,7 +6613,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>382</v>
+        <v>178</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6636,7 +6643,7 @@
         <v>81</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>81</v>
@@ -6647,42 +6654,46 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>81</v>
+        <v>382</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>190</v>
+        <v>138</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="M40" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+      <c r="N40" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
       </c>
@@ -6706,13 +6717,13 @@
         <v>81</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>300</v>
+        <v>81</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>386</v>
+        <v>81</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>387</v>
+        <v>81</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
@@ -6730,19 +6741,19 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>388</v>
+        <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>81</v>
@@ -6754,13 +6765,13 @@
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>389</v>
+        <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>293</v>
+        <v>136</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>81</v>
@@ -6771,10 +6782,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6785,7 +6796,7 @@
         <v>82</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>81</v>
@@ -6797,13 +6808,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>391</v>
+        <v>190</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6830,13 +6841,13 @@
         <v>81</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>81</v>
+        <v>300</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>81</v>
+        <v>389</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>81</v>
+        <v>390</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>81</v>
@@ -6854,16 +6865,16 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>105</v>
@@ -6878,13 +6889,13 @@
         <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>81</v>
+        <v>243</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>394</v>
+        <v>293</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>81</v>
@@ -6895,10 +6906,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6909,7 +6920,7 @@
         <v>82</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>81</v>
@@ -6921,13 +6932,13 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>190</v>
+        <v>394</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6954,13 +6965,13 @@
         <v>81</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>300</v>
+        <v>81</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>398</v>
+        <v>81</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>399</v>
+        <v>81</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>81</v>
@@ -6978,16 +6989,16 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>81</v>
+        <v>391</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>105</v>
@@ -7008,7 +7019,7 @@
         <v>81</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>81</v>
@@ -7019,10 +7030,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7033,7 +7044,7 @@
         <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>81</v>
@@ -7045,17 +7056,15 @@
         <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>371</v>
+        <v>190</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -7080,13 +7089,13 @@
         <v>81</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>81</v>
+        <v>300</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>81</v>
+        <v>401</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>81</v>
+        <v>402</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>81</v>
@@ -7104,19 +7113,19 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>405</v>
+        <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>81</v>
@@ -7134,7 +7143,7 @@
         <v>81</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>81</v>
@@ -7145,10 +7154,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7159,7 +7168,7 @@
         <v>82</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>81</v>
@@ -7171,15 +7180,17 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>169</v>
+        <v>374</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>170</v>
+        <v>405</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -7228,19 +7239,19 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>172</v>
+        <v>404</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>81</v>
+        <v>408</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>81</v>
@@ -7258,7 +7269,7 @@
         <v>81</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>173</v>
+        <v>409</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>81</v>
@@ -7269,21 +7280,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>81</v>
@@ -7295,17 +7306,15 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -7354,19 +7363,19 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>144</v>
+        <v>81</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>81</v>
@@ -7395,14 +7404,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>379</v>
+        <v>153</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7415,26 +7424,24 @@
         <v>81</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>138</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>380</v>
+        <v>175</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>381</v>
+        <v>176</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="O46" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>81</v>
       </c>
@@ -7482,7 +7489,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>382</v>
+        <v>178</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7512,7 +7519,7 @@
         <v>81</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>81</v>
@@ -7523,14 +7530,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>81</v>
+        <v>382</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7543,22 +7550,26 @@
         <v>81</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>190</v>
+        <v>138</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>411</v>
+        <v>383</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
       </c>
@@ -7582,13 +7593,13 @@
         <v>81</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>300</v>
+        <v>81</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>413</v>
+        <v>81</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>414</v>
+        <v>81</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>81</v>
@@ -7606,7 +7617,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>410</v>
+        <v>385</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7615,10 +7626,10 @@
         <v>83</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>415</v>
+        <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>81</v>
@@ -7627,19 +7638,19 @@
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>416</v>
+        <v>81</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>263</v>
+        <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>417</v>
+        <v>136</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>418</v>
+        <v>81</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>81</v>
@@ -7647,10 +7658,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7673,13 +7684,13 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>420</v>
+        <v>190</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7706,13 +7717,13 @@
         <v>81</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>81</v>
+        <v>300</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>81</v>
+        <v>416</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>81</v>
+        <v>417</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>81</v>
@@ -7730,7 +7741,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -7739,7 +7750,7 @@
         <v>83</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>105</v>
@@ -7751,19 +7762,19 @@
         <v>81</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>81</v>
+        <v>419</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>81</v>
+        <v>263</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>81</v>
@@ -7771,10 +7782,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7794,16 +7805,16 @@
         <v>81</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7854,7 +7865,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -7863,7 +7874,7 @@
         <v>83</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>81</v>
+        <v>418</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>105</v>
@@ -7875,26 +7886,150 @@
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP49" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AQ49" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AR49" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K50" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AN49" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO49" t="s" s="2">
+      <c r="L50" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="AP49" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AQ49" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR49" t="s" s="2">
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AP50" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AQ50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR50" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR49">
+  <autoFilter ref="A1:AR50">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7904,7 +8039,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI48">
+  <conditionalFormatting sqref="A2:AI49">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file V POV (#9000010.07) to us-core-condition-encounter-diagnosis</t>
+    <t>This StructureDefinition contains the maps for VistA file V POV (9000010.07) to us-core-condition-encounter-diagnosis</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -684,7 +684,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>346: source value from V POV - IEN (#9000010.07-.001)</t>
+    <t>346: source value from V POV - IEN (9000010.07-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -759,7 +759,7 @@
 con-4con-5</t>
   </si>
   <si>
-    <t>604: terminologyMaps using VF_encounterProblemStatus on V POV - MODIFIER (#9000010.07-.06)</t>
+    <t>604: terminologyMaps using VF_encounterProblemStatus on V POV - MODIFIER (9000010.07-.06)</t>
   </si>
   <si>
     <t>Outpat.VDiagnosis.Modifier,Outpat.WorkloadVDiagnosis.Modifier</t>
@@ -801,7 +801,7 @@
 con-5</t>
   </si>
   <si>
-    <t>606: terminologyMaps using VF_encounterProblemVerificationStatus on V POV - MODIFIER (#9000010.07-.06)</t>
+    <t>606: terminologyMaps using VF_encounterProblemVerificationStatus on V POV - MODIFIER (9000010.07-.06)</t>
   </si>
   <si>
     <t>&lt; 410514004 |Finding context value|</t>
@@ -920,7 +920,7 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-condition-code</t>
   </si>
   <si>
-    <t>1613: source value from V POV - POV &gt; ICD DIAGNOSIS (#9000010.07-.01 &gt; 80-)</t>
+    <t>1613: source value from V POV - POV &gt; ICD DIAGNOSIS (9000010.07-.01 &gt; 80-)</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1000,7 +1000,7 @@
     <t>Group is typically used for veterinary or public health use cases.</t>
   </si>
   <si>
-    <t>1611: reference from V POV - PATIENT NAME (#9000010.07-.02)</t>
+    <t>1611: reference from V POV - PATIENT NAME (9000010.07-.02)</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1031,7 +1031,7 @@
     <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter. This record indicates the encounter this particular record is associated with.  In the case of a "new" diagnosis reflecting ongoing/revised information about the condition, this might be distinct from the first encounter in which the underlying condition was first "known".</t>
   </si>
   <si>
-    <t>368: source value from V POV - VISIT (#9000010.07-.03)</t>
+    <t>368: source value from V POV - VISIT (9000010.07-.03)</t>
   </si>
   <si>
     <t>Outpat.VDiagnosis.VisitDateTime,Outpat.WorkloadVDiagnosis.VisitDateTime</t>
@@ -1091,7 +1091,7 @@
 </t>
   </si>
   <si>
-    <t>370: source value from V POV - DATE OF INJURY (#9000010.07-.13)</t>
+    <t>370: source value from V POV - DATE OF INJURY (9000010.07-.13)</t>
   </si>
   <si>
     <t>Outpat.VDiagnosis.InjuryDateTime,Outpat.WorkloadVDiagnosis.InjuryDateTime</t>
@@ -1137,7 +1137,7 @@
     <t>The recordedDate represents when this particular Condition record was created in the system, which is often a system-generated date.</t>
   </si>
   <si>
-    <t>372: source value from V POV - VISIT &gt; VISIT - VISIT/ADMIT DATE&amp;TIME (#9000010.07-.03 &gt; 9000010-.01)</t>
+    <t>372: source value from V POV - VISIT &gt; VISIT - VISIT/ADMIT DATE&amp;TIME (9000010.07-.03 &gt; 9000010-.01)</t>
   </si>
   <si>
     <t>Outpat.VDiagnosis.VisitDateTime,Outpat.WorkloadVDiagnosis.VisitDateTime
@@ -1732,7 +1732,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="102.29296875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="100.7578125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="73.890625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2030" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2030" uniqueCount="435">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -921,6 +921,9 @@
   </si>
   <si>
     <t>1613: source value from V POV - POV &gt; ICD DIAGNOSIS (9000010.07-.01 &gt; 80-)</t>
+  </si>
+  <si>
+    <t>Outpat.VDiagnosis.ICDIEN,Outpat.WorkloadVDiagnosis.ICDIEN</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1003,6 +1006,9 @@
     <t>1611: reference from V POV - PATIENT NAME (9000010.07-.02)</t>
   </si>
   <si>
+    <t>Outpat.VDiagnosis.PatientIEN,Outpat.WorkloadVDiagnosis.PatientIEN</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -1034,7 +1040,7 @@
     <t>368: source value from V POV - VISIT (9000010.07-.03)</t>
   </si>
   <si>
-    <t>Outpat.VDiagnosis.VisitDateTime,Outpat.WorkloadVDiagnosis.VisitDateTime</t>
+    <t>Outpat.VDiagnosis.VisitDateTime,Outpat.VDiagnosis.VisitIEN,Outpat.WorkloadVDiagnosis.VisitDateTime,Outpat.WorkloadVDiagnosis.VisitIEN</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1140,8 +1146,8 @@
     <t>372: source value from V POV - VISIT &gt; VISIT - VISIT/ADMIT DATE&amp;TIME (9000010.07-.03 &gt; 9000010-.01)</t>
   </si>
   <si>
-    <t>Outpat.VDiagnosis.VisitDateTime,Outpat.WorkloadVDiagnosis.VisitDateTime
-Outpat.Visit.VisitDateTime,Outpat.Workload.VisitDateTime</t>
+    <t>Outpat.VDiagnosis.VisitDateTime,Outpat.VDiagnosis.VisitIEN,Outpat.WorkloadVDiagnosis.VisitDateTime,Outpat.WorkloadVDiagnosis.VisitIEN
+Immun.ImmunizationContraRefusalEvent.VisitDateTime,Outpat.Visit.VisitDateTime,Outpat.VisitLogic.VisitDateTime,Outpat.Workload.VisitDateTime</t>
   </si>
   <si>
     <t>REL-11</t>
@@ -1733,7 +1739,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="100.7578125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="73.890625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="136.5078125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="68.20703125" customWidth="true" bestFit="true"/>
@@ -5003,33 +5009,33 @@
         <v>289</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>81</v>
+        <v>290</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5055,13 +5061,13 @@
         <v>190</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5087,13 +5093,13 @@
         <v>81</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
@@ -5111,7 +5117,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5135,31 +5141,31 @@
         <v>81</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5178,17 +5184,17 @@
         <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -5237,7 +5243,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>93</v>
@@ -5252,25 +5258,25 @@
         <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>81</v>
+        <v>314</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>81</v>
@@ -5278,10 +5284,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5304,16 +5310,16 @@
         <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5363,7 +5369,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5378,25 +5384,25 @@
         <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>81</v>
@@ -5404,10 +5410,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5430,16 +5436,16 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5477,7 +5483,7 @@
         <v>81</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AC30" s="2"/>
       <c r="AD30" t="s" s="2">
@@ -5487,7 +5493,7 @@
         <v>142</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5508,19 +5514,19 @@
         <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>81</v>
@@ -5528,13 +5534,13 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>81</v>
@@ -5556,16 +5562,16 @@
         <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5615,7 +5621,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -5630,25 +5636,25 @@
         <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>81</v>
@@ -5656,10 +5662,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5682,16 +5688,16 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5729,7 +5735,7 @@
         <v>81</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AC32" s="2"/>
       <c r="AD32" t="s" s="2">
@@ -5739,7 +5745,7 @@
         <v>142</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -5748,7 +5754,7 @@
         <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>105</v>
@@ -5769,10 +5775,10 @@
         <v>81</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>81</v>
@@ -5780,13 +5786,13 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>81</v>
@@ -5808,16 +5814,16 @@
         <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5867,7 +5873,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -5876,13 +5882,13 @@
         <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>81</v>
@@ -5897,10 +5903,10 @@
         <v>81</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>81</v>
@@ -5908,10 +5914,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5934,13 +5940,13 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5991,7 +5997,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6006,10 +6012,10 @@
         <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>81</v>
@@ -6018,13 +6024,13 @@
         <v>81</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>81</v>
@@ -6032,10 +6038,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6058,13 +6064,13 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6115,7 +6121,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6145,10 +6151,10 @@
         <v>81</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>81</v>
@@ -6156,10 +6162,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6182,13 +6188,13 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6239,7 +6245,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6266,13 +6272,13 @@
         <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>81</v>
@@ -6280,10 +6286,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6306,13 +6312,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6363,7 +6369,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6375,7 +6381,7 @@
         <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>81</v>
@@ -6393,7 +6399,7 @@
         <v>81</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>81</v>
@@ -6404,10 +6410,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6528,10 +6534,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6654,14 +6660,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6683,10 +6689,10 @@
         <v>138</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>156</v>
@@ -6741,7 +6747,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -6782,10 +6788,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6811,10 +6817,10 @@
         <v>190</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6841,13 +6847,13 @@
         <v>81</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>81</v>
@@ -6865,7 +6871,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -6874,7 +6880,7 @@
         <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>105</v>
@@ -6889,13 +6895,13 @@
         <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>243</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>81</v>
@@ -6906,10 +6912,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6932,13 +6938,13 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6989,7 +6995,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -6998,7 +7004,7 @@
         <v>83</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>105</v>
@@ -7019,7 +7025,7 @@
         <v>81</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>81</v>
@@ -7030,10 +7036,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7059,10 +7065,10 @@
         <v>190</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7089,13 +7095,13 @@
         <v>81</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>81</v>
@@ -7113,7 +7119,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7143,7 +7149,7 @@
         <v>81</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>81</v>
@@ -7154,10 +7160,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7180,16 +7186,16 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7239,7 +7245,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7251,7 +7257,7 @@
         <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>81</v>
@@ -7269,7 +7275,7 @@
         <v>81</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>81</v>
@@ -7280,10 +7286,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7404,10 +7410,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7530,14 +7536,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7559,10 +7565,10 @@
         <v>138</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>156</v>
@@ -7617,7 +7623,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7658,10 +7664,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7687,10 +7693,10 @@
         <v>190</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7717,13 +7723,13 @@
         <v>81</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>81</v>
@@ -7741,7 +7747,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -7750,7 +7756,7 @@
         <v>83</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>105</v>
@@ -7762,7 +7768,7 @@
         <v>81</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>263</v>
@@ -7771,10 +7777,10 @@
         <v>81</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>81</v>
@@ -7782,10 +7788,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7808,13 +7814,13 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7865,7 +7871,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -7874,7 +7880,7 @@
         <v>83</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>105</v>
@@ -7895,10 +7901,10 @@
         <v>81</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>81</v>
@@ -7906,10 +7912,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7932,13 +7938,13 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7989,7 +7995,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8010,16 +8016,16 @@
         <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2030" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2030" uniqueCount="437">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1170,6 +1170,12 @@
   </si>
   <si>
     <t>Individual who recorded the record and takes responsibility for its content.</t>
+  </si>
+  <si>
+    <t>1833: reference from V POV - ENCOUNTER PROVIDER (9000010.07-1204)</t>
+  </si>
+  <si>
+    <t>Outpat.VDiagnosis.EncounterProviderIEN,Outpat.WorkloadVDiagnosis.EncounterProviderIEN</t>
   </si>
   <si>
     <t>.participation[typeCode=AUT].role</t>
@@ -6055,7 +6061,7 @@
         <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>81</v>
@@ -6136,10 +6142,10 @@
         <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>81</v>
+        <v>367</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>81</v>
+        <v>368</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>81</v>
@@ -6151,10 +6157,10 @@
         <v>81</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>81</v>
@@ -6162,10 +6168,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6191,10 +6197,10 @@
         <v>364</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6245,7 +6251,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6272,13 +6278,13 @@
         <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>81</v>
@@ -6286,10 +6292,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6312,13 +6318,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6369,7 +6375,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6381,7 +6387,7 @@
         <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>81</v>
@@ -6399,7 +6405,7 @@
         <v>81</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>81</v>
@@ -6410,10 +6416,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6534,10 +6540,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6660,14 +6666,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6689,10 +6695,10 @@
         <v>138</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>156</v>
@@ -6747,7 +6753,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -6788,10 +6794,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6817,10 +6823,10 @@
         <v>190</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6850,10 +6856,10 @@
         <v>301</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>81</v>
@@ -6871,7 +6877,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -6880,7 +6886,7 @@
         <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>105</v>
@@ -6895,7 +6901,7 @@
         <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>243</v>
@@ -6912,10 +6918,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6938,13 +6944,13 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6995,7 +7001,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7004,7 +7010,7 @@
         <v>83</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>105</v>
@@ -7025,7 +7031,7 @@
         <v>81</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>81</v>
@@ -7036,10 +7042,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7065,10 +7071,10 @@
         <v>190</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7098,10 +7104,10 @@
         <v>301</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>81</v>
@@ -7119,7 +7125,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7149,7 +7155,7 @@
         <v>81</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>81</v>
@@ -7160,10 +7166,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7186,16 +7192,16 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7245,7 +7251,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7257,7 +7263,7 @@
         <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>81</v>
@@ -7275,7 +7281,7 @@
         <v>81</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>81</v>
@@ -7286,10 +7292,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7410,10 +7416,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7536,14 +7542,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7565,10 +7571,10 @@
         <v>138</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>156</v>
@@ -7623,7 +7629,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7664,10 +7670,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7693,10 +7699,10 @@
         <v>190</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7726,10 +7732,10 @@
         <v>301</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>81</v>
@@ -7747,7 +7753,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -7756,7 +7762,7 @@
         <v>83</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>105</v>
@@ -7768,7 +7774,7 @@
         <v>81</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>263</v>
@@ -7777,10 +7783,10 @@
         <v>81</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>81</v>
@@ -7788,10 +7794,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7814,13 +7820,13 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7871,7 +7877,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -7880,7 +7886,7 @@
         <v>83</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>105</v>
@@ -7901,10 +7907,10 @@
         <v>81</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>81</v>
@@ -7912,10 +7918,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7938,13 +7944,13 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7995,7 +8001,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8016,16 +8022,16 @@
         <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$61</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2030" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2472" uniqueCount="501">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -654,10 +654,16 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
+    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+  </si>
+  <si>
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
     <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>346-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>
@@ -951,6 +957,195 @@
   </si>
   <si>
     <t>246090004</t>
+  </si>
+  <si>
+    <t>Condition.code.id</t>
+  </si>
+  <si>
+    <t>Condition.code.extension</t>
+  </si>
+  <si>
+    <t>Condition.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.id</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>1613-1: undefined</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>1613-2: source value from V POV - POV &gt; ICD DIAGNOSIS - CODE NUMBER (9000010.07-.01 &gt; 80-.01)</t>
+  </si>
+  <si>
+    <t>Outpat.VDiagnosis.ICDIEN,Outpat.WorkloadVDiagnosis.ICDIEN
+Dim.ICD10.ICD10Code,Dim.ICD9.ICD9Code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Condition.code.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Condition.bodySite</t>
@@ -1706,7 +1901,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR50"/>
+  <dimension ref="A1:AR61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.5390625" customWidth="true" bestFit="true"/>
@@ -3799,7 +3994,7 @@
         <v>93</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>81</v>
@@ -3830,10 +4025,10 @@
         <v>81</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>81</v>
+        <v>205</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>81</v>
@@ -3869,7 +4064,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>82</v>
@@ -3884,7 +4079,7 @@
         <v>105</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>81</v>
+        <v>208</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>81</v>
@@ -3896,10 +4091,10 @@
         <v>81</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>81</v>
@@ -3910,10 +4105,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3939,13 +4134,13 @@
         <v>169</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3959,7 +4154,7 @@
         <v>81</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>81</v>
@@ -3995,7 +4190,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4010,7 +4205,7 @@
         <v>105</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>81</v>
@@ -4022,10 +4217,10 @@
         <v>81</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>81</v>
@@ -4036,10 +4231,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4062,13 +4257,13 @@
         <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4119,7 +4314,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4146,10 +4341,10 @@
         <v>81</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>81</v>
@@ -4160,10 +4355,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4186,16 +4381,16 @@
         <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4245,7 +4440,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4272,10 +4467,10 @@
         <v>81</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>81</v>
@@ -4286,10 +4481,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4315,13 +4510,13 @@
         <v>190</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4351,7 +4546,7 @@
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>81</v>
@@ -4369,7 +4564,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -4378,31 +4573,31 @@
         <v>93</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AR21" t="s" s="2">
         <v>81</v>
@@ -4410,10 +4605,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4439,13 +4634,13 @@
         <v>190</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4475,7 +4670,7 @@
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>81</v>
@@ -4493,7 +4688,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -4502,42 +4697,42 @@
         <v>93</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4563,13 +4758,13 @@
         <v>190</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4598,16 +4793,16 @@
         <v>195</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -4617,7 +4812,7 @@
         <v>142</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -4641,16 +4836,16 @@
         <v>81</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>81</v>
@@ -4658,13 +4853,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>81</v>
@@ -4689,13 +4884,13 @@
         <v>190</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4706,7 +4901,7 @@
         <v>81</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>81</v>
@@ -4724,28 +4919,28 @@
         <v>195</v>
       </c>
       <c r="Y24" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -4760,7 +4955,7 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>81</v>
@@ -4769,16 +4964,16 @@
         <v>81</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>81</v>
@@ -4786,10 +4981,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4815,13 +5010,13 @@
         <v>190</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4850,28 +5045,28 @@
         <v>117</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -4895,31 +5090,31 @@
         <v>81</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4941,14 +5136,14 @@
         <v>190</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -4976,10 +5171,10 @@
         <v>195</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -4997,7 +5192,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5012,36 +5207,36 @@
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5052,7 +5247,7 @@
         <v>82</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>81</v>
@@ -5061,20 +5256,18 @@
         <v>81</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>298</v>
+        <v>170</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5099,13 +5292,13 @@
         <v>81</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>301</v>
+        <v>81</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>302</v>
+        <v>81</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>303</v>
+        <v>81</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
@@ -5123,19 +5316,19 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>297</v>
+        <v>172</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>81</v>
@@ -5147,61 +5340,61 @@
         <v>81</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>304</v>
+        <v>81</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>305</v>
+        <v>173</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>306</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>308</v>
+        <v>153</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>309</v>
+        <v>138</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>310</v>
+        <v>175</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>81</v>
       </c>
@@ -5237,52 +5430,52 @@
         <v>81</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>81</v>
+        <v>177</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>307</v>
+        <v>178</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>313</v>
+        <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>314</v>
+        <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>315</v>
+        <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>316</v>
+        <v>81</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>317</v>
+        <v>173</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>318</v>
+        <v>81</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>81</v>
@@ -5290,10 +5483,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5304,10 +5497,10 @@
         <v>82</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>81</v>
@@ -5316,18 +5509,20 @@
         <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>81</v>
       </c>
@@ -5375,13 +5570,13 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>81</v>
@@ -5390,25 +5585,25 @@
         <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>325</v>
+        <v>81</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>326</v>
+        <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>329</v>
+        <v>81</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>81</v>
@@ -5416,10 +5611,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5433,26 +5628,24 @@
         <v>93</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>331</v>
+        <v>169</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>332</v>
+        <v>170</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>81</v>
@@ -5489,17 +5682,19 @@
         <v>81</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="AC30" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>142</v>
+        <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>330</v>
+        <v>172</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5511,7 +5706,7 @@
         <v>81</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>81</v>
@@ -5520,19 +5715,19 @@
         <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>336</v>
+        <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>337</v>
+        <v>81</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>338</v>
+        <v>173</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>339</v>
+        <v>81</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>81</v>
@@ -5540,44 +5735,42 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>340</v>
+        <v>311</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>342</v>
+        <v>138</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>332</v>
+        <v>175</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>333</v>
+        <v>176</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>334</v>
+        <v>156</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5615,52 +5808,52 @@
         <v>81</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>81</v>
+        <v>177</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>330</v>
+        <v>178</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>343</v>
+        <v>81</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>344</v>
+        <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>336</v>
+        <v>81</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>337</v>
+        <v>81</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>338</v>
+        <v>173</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>339</v>
+        <v>81</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>81</v>
@@ -5668,10 +5861,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>345</v>
+        <v>312</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>345</v>
+        <v>312</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5691,21 +5884,23 @@
         <v>81</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>331</v>
+        <v>107</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>346</v>
+        <v>313</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>347</v>
+        <v>314</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>316</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>81</v>
       </c>
@@ -5741,17 +5936,19 @@
         <v>81</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="AC32" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>142</v>
+        <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>345</v>
+        <v>317</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -5760,13 +5957,13 @@
         <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>349</v>
+        <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>81</v>
+        <v>318</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>81</v>
@@ -5778,13 +5975,13 @@
         <v>81</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>81</v>
+        <v>319</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>351</v>
+        <v>81</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>81</v>
@@ -5792,14 +5989,12 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>352</v>
+        <v>321</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>81</v>
       </c>
@@ -5811,25 +6006,25 @@
         <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J33" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="K33" t="s" s="2">
-        <v>342</v>
+        <v>169</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>346</v>
+        <v>322</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>347</v>
+        <v>323</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>348</v>
+        <v>324</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5879,7 +6074,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -5888,13 +6083,13 @@
         <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>349</v>
+        <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>354</v>
+        <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>81</v>
@@ -5906,13 +6101,13 @@
         <v>81</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>81</v>
+        <v>326</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>350</v>
+        <v>327</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>351</v>
+        <v>81</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>81</v>
@@ -5920,10 +6115,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>355</v>
+        <v>328</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>355</v>
+        <v>328</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5946,16 +6141,18 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>342</v>
+        <v>113</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>356</v>
+        <v>329</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>357</v>
+        <v>330</v>
       </c>
       <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+      <c r="O34" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
       </c>
@@ -6003,7 +6200,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6018,10 +6215,10 @@
         <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>358</v>
+        <v>333</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>359</v>
+        <v>334</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>81</v>
@@ -6030,13 +6227,13 @@
         <v>81</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>360</v>
+        <v>335</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>361</v>
+        <v>336</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>362</v>
+        <v>81</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>81</v>
@@ -6044,10 +6241,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>363</v>
+        <v>337</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>363</v>
+        <v>337</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6061,7 +6258,7 @@
         <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>81</v>
@@ -6070,16 +6267,18 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>364</v>
+        <v>169</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>365</v>
+        <v>338</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>366</v>
+        <v>339</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
       </c>
@@ -6127,7 +6326,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>363</v>
+        <v>341</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6142,10 +6341,10 @@
         <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>367</v>
+        <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>368</v>
+        <v>81</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>81</v>
@@ -6154,13 +6353,13 @@
         <v>81</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>81</v>
+        <v>342</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>369</v>
+        <v>343</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>370</v>
+        <v>81</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>81</v>
@@ -6168,10 +6367,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>371</v>
+        <v>344</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>371</v>
+        <v>344</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6194,16 +6393,20 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>364</v>
+        <v>345</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>372</v>
+        <v>346</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
       </c>
@@ -6251,7 +6454,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>371</v>
+        <v>350</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6278,13 +6481,13 @@
         <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>374</v>
+        <v>351</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>375</v>
+        <v>352</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>376</v>
+        <v>81</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>81</v>
@@ -6292,10 +6495,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6306,7 +6509,7 @@
         <v>82</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>81</v>
@@ -6315,19 +6518,23 @@
         <v>81</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>378</v>
+        <v>169</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>379</v>
+        <v>354</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
       </c>
@@ -6375,19 +6582,19 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>377</v>
+        <v>358</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>381</v>
+        <v>105</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>81</v>
@@ -6402,10 +6609,10 @@
         <v>81</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>81</v>
+        <v>359</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>382</v>
+        <v>360</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>81</v>
@@ -6416,10 +6623,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>383</v>
+        <v>361</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>383</v>
+        <v>361</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6430,7 +6637,7 @@
         <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>81</v>
@@ -6439,18 +6646,20 @@
         <v>81</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>170</v>
+        <v>362</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>81</v>
@@ -6475,13 +6684,13 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>81</v>
+        <v>365</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>81</v>
+        <v>366</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>81</v>
+        <v>367</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -6499,19 +6708,19 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>172</v>
+        <v>361</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>81</v>
@@ -6523,61 +6732,61 @@
         <v>81</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>81</v>
+        <v>368</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>173</v>
+        <v>369</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>81</v>
+        <v>370</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>153</v>
+        <v>372</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>138</v>
+        <v>373</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>175</v>
+        <v>374</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
       </c>
@@ -6625,40 +6834,40 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>178</v>
+        <v>371</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>81</v>
+        <v>377</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>81</v>
+        <v>378</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>81</v>
+        <v>379</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>81</v>
+        <v>380</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>173</v>
+        <v>381</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>81</v>
+        <v>382</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>81</v>
@@ -6666,46 +6875,44 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>386</v>
+        <v>81</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>138</v>
+        <v>384</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M40" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>81</v>
       </c>
@@ -6753,40 +6960,40 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AG40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AM40" t="s" s="2">
-        <v>81</v>
+        <v>390</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>81</v>
+        <v>391</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>136</v>
+        <v>392</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>81</v>
+        <v>393</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>81</v>
@@ -6794,10 +7001,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6811,24 +7018,26 @@
         <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>190</v>
+        <v>395</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6853,31 +7062,29 @@
         <v>81</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>301</v>
+        <v>81</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>393</v>
+        <v>81</v>
       </c>
       <c r="Z41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AC41" s="2"/>
+      <c r="AD41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -6886,7 +7093,7 @@
         <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>395</v>
+        <v>81</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>105</v>
@@ -6898,19 +7105,19 @@
         <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>81</v>
+        <v>400</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>396</v>
+        <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>243</v>
+        <v>401</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>294</v>
+        <v>402</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>81</v>
+        <v>403</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>81</v>
@@ -6918,12 +7125,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="D42" t="s" s="2">
         <v>81</v>
       </c>
@@ -6932,27 +7141,29 @@
         <v>82</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="L42" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -7001,40 +7212,40 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>395</v>
+        <v>81</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>81</v>
+        <v>407</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>81</v>
+        <v>408</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>81</v>
+        <v>400</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>81</v>
+        <v>401</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>81</v>
+        <v>403</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>81</v>
@@ -7042,10 +7253,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7059,7 +7270,7 @@
         <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>81</v>
@@ -7068,15 +7279,17 @@
         <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>190</v>
+        <v>395</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -7101,31 +7314,29 @@
         <v>81</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>301</v>
+        <v>81</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>405</v>
+        <v>81</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>406</v>
+        <v>81</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7134,7 +7345,7 @@
         <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>81</v>
+        <v>413</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>105</v>
@@ -7155,10 +7366,10 @@
         <v>81</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>81</v>
+        <v>415</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>81</v>
@@ -7166,12 +7377,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>409</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>81</v>
       </c>
@@ -7180,10 +7393,10 @@
         <v>82</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>81</v>
@@ -7192,16 +7405,16 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>378</v>
+        <v>406</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7251,22 +7464,22 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>81</v>
+        <v>413</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>412</v>
+        <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>81</v>
+        <v>418</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>81</v>
@@ -7281,10 +7494,10 @@
         <v>81</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>81</v>
+        <v>415</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>81</v>
@@ -7292,10 +7505,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7309,22 +7522,22 @@
         <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>169</v>
+        <v>406</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>170</v>
+        <v>420</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>171</v>
+        <v>421</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7375,7 +7588,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>172</v>
+        <v>419</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7387,13 +7600,13 @@
         <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>81</v>
+        <v>422</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>81</v>
@@ -7402,13 +7615,13 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>81</v>
+        <v>424</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>173</v>
+        <v>425</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>81</v>
+        <v>426</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>81</v>
@@ -7416,43 +7629,41 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>138</v>
+        <v>428</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>175</v>
+        <v>429</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -7501,25 +7712,25 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>178</v>
+        <v>427</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>81</v>
+        <v>431</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>81</v>
+        <v>432</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
@@ -7531,10 +7742,10 @@
         <v>81</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>173</v>
+        <v>433</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>81</v>
+        <v>434</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>81</v>
@@ -7542,46 +7753,42 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>416</v>
+        <v>435</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>416</v>
+        <v>435</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>386</v>
+        <v>81</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>138</v>
+        <v>428</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>387</v>
+        <v>436</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>81</v>
       </c>
@@ -7629,19 +7836,19 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>389</v>
+        <v>435</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>81</v>
@@ -7656,13 +7863,13 @@
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>81</v>
+        <v>438</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>136</v>
+        <v>439</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>81</v>
+        <v>440</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>81</v>
@@ -7670,10 +7877,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>417</v>
+        <v>441</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>417</v>
+        <v>441</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7693,16 +7900,16 @@
         <v>81</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>190</v>
+        <v>442</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>418</v>
+        <v>443</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>419</v>
+        <v>444</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7729,13 +7936,13 @@
         <v>81</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>301</v>
+        <v>81</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>420</v>
+        <v>81</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>421</v>
+        <v>81</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>81</v>
@@ -7753,7 +7960,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>417</v>
+        <v>441</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -7762,10 +7969,10 @@
         <v>83</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>422</v>
+        <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>105</v>
+        <v>445</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>81</v>
@@ -7774,19 +7981,19 @@
         <v>81</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>263</v>
+        <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>424</v>
+        <v>446</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>425</v>
+        <v>81</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>81</v>
@@ -7794,10 +8001,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7808,7 +8015,7 @@
         <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>81</v>
@@ -7817,16 +8024,16 @@
         <v>81</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>427</v>
+        <v>169</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>428</v>
+        <v>170</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>429</v>
+        <v>171</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7877,19 +8084,19 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>426</v>
+        <v>172</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>422</v>
+        <v>81</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>81</v>
@@ -7907,10 +8114,10 @@
         <v>81</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>401</v>
+        <v>173</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>425</v>
+        <v>81</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>81</v>
@@ -7918,14 +8125,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7944,15 +8151,17 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>431</v>
+        <v>138</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>432</v>
+        <v>175</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>81</v>
@@ -8001,7 +8210,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>430</v>
+        <v>178</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8013,35 +8222,1411 @@
         <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP50" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AQ50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR50" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="P51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP51" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AQ51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR51" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AK50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AQ50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR50" t="s" s="2">
+      <c r="AK52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AP52" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AQ52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR52" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP53" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AQ53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR53" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AQ54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR54" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AQ55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR55" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AQ56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR56" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP57" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AQ57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR57" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AQ58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR58" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AQ59" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AR59" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AQ60" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AR60" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR61" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR50">
+  <autoFilter ref="A1:AR61">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8051,7 +9636,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI49">
+  <conditionalFormatting sqref="A2:AI60">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2472" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2472" uniqueCount="502">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1014,10 +1014,13 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
+    <t>urn:see-termmap-in-mapParameter</t>
+  </si>
+  <si>
     <t>Coding.system</t>
   </si>
   <si>
-    <t>1613-1: undefined</t>
+    <t>1613-1: fixed value = urn:see-termmap-in-mapParameter</t>
   </si>
   <si>
     <t>C*E.3</t>
@@ -5909,7 +5912,7 @@
         <v>81</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>81</v>
+        <v>317</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>81</v>
@@ -5948,7 +5951,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -5963,7 +5966,7 @@
         <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>81</v>
@@ -5975,10 +5978,10 @@
         <v>81</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>81</v>
@@ -5989,10 +5992,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6018,13 +6021,13 @@
         <v>169</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6074,7 +6077,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6101,10 +6104,10 @@
         <v>81</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>81</v>
@@ -6115,10 +6118,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6144,14 +6147,14 @@
         <v>113</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
@@ -6200,7 +6203,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6215,10 +6218,10 @@
         <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>81</v>
@@ -6227,10 +6230,10 @@
         <v>81</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>81</v>
@@ -6241,10 +6244,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6270,14 +6273,14 @@
         <v>169</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -6326,7 +6329,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6353,10 +6356,10 @@
         <v>81</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>81</v>
@@ -6367,10 +6370,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6393,19 +6396,19 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6454,7 +6457,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6481,10 +6484,10 @@
         <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>81</v>
@@ -6495,10 +6498,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6524,16 +6527,16 @@
         <v>169</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6582,7 +6585,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6609,10 +6612,10 @@
         <v>81</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>81</v>
@@ -6623,10 +6626,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6652,13 +6655,13 @@
         <v>190</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6684,13 +6687,13 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -6708,7 +6711,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6732,31 +6735,31 @@
         <v>81</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6775,17 +6778,17 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6834,7 +6837,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>93</v>
@@ -6849,25 +6852,25 @@
         <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>81</v>
@@ -6875,10 +6878,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6901,16 +6904,16 @@
         <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6960,7 +6963,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -6975,25 +6978,25 @@
         <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>81</v>
@@ -7001,10 +7004,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7027,16 +7030,16 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7074,7 +7077,7 @@
         <v>81</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
@@ -7084,7 +7087,7 @@
         <v>142</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7105,19 +7108,19 @@
         <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>81</v>
@@ -7125,13 +7128,13 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>81</v>
@@ -7153,16 +7156,16 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7212,7 +7215,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7227,25 +7230,25 @@
         <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>81</v>
@@ -7253,10 +7256,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7279,16 +7282,16 @@
         <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7326,7 +7329,7 @@
         <v>81</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
@@ -7336,7 +7339,7 @@
         <v>142</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7345,7 +7348,7 @@
         <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>105</v>
@@ -7366,10 +7369,10 @@
         <v>81</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>81</v>
@@ -7377,13 +7380,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>81</v>
@@ -7405,16 +7408,16 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7464,7 +7467,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7473,13 +7476,13 @@
         <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>81</v>
@@ -7494,10 +7497,10 @@
         <v>81</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>81</v>
@@ -7505,10 +7508,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7531,13 +7534,13 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7588,7 +7591,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7603,10 +7606,10 @@
         <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>81</v>
@@ -7615,13 +7618,13 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>81</v>
@@ -7629,10 +7632,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7655,13 +7658,13 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7712,7 +7715,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7727,10 +7730,10 @@
         <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
@@ -7742,10 +7745,10 @@
         <v>81</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>81</v>
@@ -7753,10 +7756,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7779,13 +7782,13 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7836,7 +7839,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7863,13 +7866,13 @@
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>81</v>
@@ -7877,10 +7880,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7903,13 +7906,13 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7960,7 +7963,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -7972,7 +7975,7 @@
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>81</v>
@@ -7990,7 +7993,7 @@
         <v>81</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>81</v>
@@ -8001,10 +8004,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8125,10 +8128,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8251,14 +8254,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8280,10 +8283,10 @@
         <v>138</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>156</v>
@@ -8338,7 +8341,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8379,10 +8382,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8408,10 +8411,10 @@
         <v>190</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8438,13 +8441,13 @@
         <v>81</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>81</v>
@@ -8462,7 +8465,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8471,7 +8474,7 @@
         <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>105</v>
@@ -8486,7 +8489,7 @@
         <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>245</v>
@@ -8503,10 +8506,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8529,13 +8532,13 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8586,7 +8589,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8595,7 +8598,7 @@
         <v>83</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>105</v>
@@ -8616,7 +8619,7 @@
         <v>81</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>81</v>
@@ -8627,10 +8630,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8656,10 +8659,10 @@
         <v>190</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8686,13 +8689,13 @@
         <v>81</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>81</v>
@@ -8710,7 +8713,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8740,7 +8743,7 @@
         <v>81</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>81</v>
@@ -8751,10 +8754,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8777,16 +8780,16 @@
         <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8836,7 +8839,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -8848,7 +8851,7 @@
         <v>81</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>81</v>
@@ -8866,7 +8869,7 @@
         <v>81</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>81</v>
@@ -8877,10 +8880,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9001,10 +9004,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9127,14 +9130,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9156,10 +9159,10 @@
         <v>138</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>156</v>
@@ -9214,7 +9217,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9255,10 +9258,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9284,10 +9287,10 @@
         <v>190</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9314,13 +9317,13 @@
         <v>81</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>81</v>
@@ -9338,7 +9341,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9347,7 +9350,7 @@
         <v>83</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>105</v>
@@ -9359,7 +9362,7 @@
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>265</v>
@@ -9368,10 +9371,10 @@
         <v>81</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>81</v>
@@ -9379,10 +9382,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9405,13 +9408,13 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9462,7 +9465,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9471,7 +9474,7 @@
         <v>83</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>105</v>
@@ -9492,10 +9495,10 @@
         <v>81</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>81</v>
@@ -9503,10 +9506,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9529,13 +9532,13 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9586,7 +9589,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9607,16 +9610,16 @@
         <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -654,7 +654,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/$fileNr</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -663,7 +663,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>346-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>346-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/$fileNr</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -654,7 +654,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/$fileNr</t>
+    <t>http://va.gov/identifiers/$Sta3n/9000010.07</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -663,7 +663,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>346-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/$fileNr</t>
+    <t>346-1: fixed value = http://va.gov/identifiers/$Sta3n/9000010.07</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1188,7 +1188,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1201,7 +1201,7 @@
     <t>Group is typically used for veterinary or public health use cases.</t>
   </si>
   <si>
-    <t>1611: reference from V POV - PATIENT NAME (9000010.07-.02)</t>
+    <t>1611: reference from V POV - PATIENT NAME &gt; PATIENT/IHS - NAME (9000010.07-.02 &gt; 9000001-.01)</t>
   </si>
   <si>
     <t>Outpat.VDiagnosis.PatientIEN,Outpat.WorkloadVDiagnosis.PatientIEN</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1201,7 +1201,7 @@
     <t>Group is typically used for veterinary or public health use cases.</t>
   </si>
   <si>
-    <t>1611: reference from V POV - PATIENT NAME &gt; PATIENT/IHS - NAME (9000010.07-.02 &gt; 9000001-.01)</t>
+    <t>1611: reference from V POV - PATIENT NAME (9000010.07-.02)</t>
   </si>
   <si>
     <t>Outpat.VDiagnosis.PatientIEN,Outpat.WorkloadVDiagnosis.PatientIEN</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2472" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2472" uniqueCount="503">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1360,29 +1360,33 @@
     <t>Condition.recorder</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
+</t>
+  </si>
+  <si>
+    <t>Who recorded the condition</t>
+  </si>
+  <si>
+    <t>Individual who recorded the record and takes responsibility for its content.</t>
+  </si>
+  <si>
+    <t>1833: reference from V POV - ENCOUNTER PROVIDER (9000010.07-1204)</t>
+  </si>
+  <si>
+    <t>Outpat.VDiagnosis.EncounterProviderIEN,Outpat.WorkloadVDiagnosis.EncounterProviderIEN</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=AUT].role</t>
+  </si>
+  <si>
+    <t>FiveWs.author</t>
+  </si>
+  <si>
+    <t>Condition.asserter</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Patient|RelatedPerson)
 </t>
-  </si>
-  <si>
-    <t>Who recorded the condition</t>
-  </si>
-  <si>
-    <t>Individual who recorded the record and takes responsibility for its content.</t>
-  </si>
-  <si>
-    <t>1833: reference from V POV - ENCOUNTER PROVIDER (9000010.07-1204)</t>
-  </si>
-  <si>
-    <t>Outpat.VDiagnosis.EncounterProviderIEN,Outpat.WorkloadVDiagnosis.EncounterProviderIEN</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=AUT].role</t>
-  </si>
-  <si>
-    <t>FiveWs.author</t>
-  </si>
-  <si>
-    <t>Condition.asserter</t>
   </si>
   <si>
     <t>Person who asserts this condition</t>
@@ -7782,13 +7786,13 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7866,13 +7870,13 @@
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>81</v>
@@ -7880,10 +7884,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7906,13 +7910,13 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7963,7 +7967,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -7975,7 +7979,7 @@
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>81</v>
@@ -7993,7 +7997,7 @@
         <v>81</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>81</v>
@@ -8004,10 +8008,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8128,10 +8132,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8254,14 +8258,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8283,10 +8287,10 @@
         <v>138</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>156</v>
@@ -8341,7 +8345,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8382,10 +8386,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8411,10 +8415,10 @@
         <v>190</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8444,10 +8448,10 @@
         <v>366</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>81</v>
@@ -8465,7 +8469,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8474,7 +8478,7 @@
         <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>105</v>
@@ -8489,7 +8493,7 @@
         <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>245</v>
@@ -8506,10 +8510,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8532,13 +8536,13 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8589,7 +8593,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8598,7 +8602,7 @@
         <v>83</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>105</v>
@@ -8619,7 +8623,7 @@
         <v>81</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>81</v>
@@ -8630,10 +8634,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8659,10 +8663,10 @@
         <v>190</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8692,10 +8696,10 @@
         <v>366</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>81</v>
@@ -8713,7 +8717,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8743,7 +8747,7 @@
         <v>81</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>81</v>
@@ -8754,10 +8758,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8780,16 +8784,16 @@
         <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8839,7 +8843,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -8851,7 +8855,7 @@
         <v>81</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>81</v>
@@ -8869,7 +8873,7 @@
         <v>81</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>81</v>
@@ -8880,10 +8884,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9004,10 +9008,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9130,14 +9134,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9159,10 +9163,10 @@
         <v>138</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>156</v>
@@ -9217,7 +9221,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9258,10 +9262,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9287,10 +9291,10 @@
         <v>190</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9320,10 +9324,10 @@
         <v>366</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>81</v>
@@ -9341,7 +9345,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9350,7 +9354,7 @@
         <v>83</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>105</v>
@@ -9362,7 +9366,7 @@
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>265</v>
@@ -9371,10 +9375,10 @@
         <v>81</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>81</v>
@@ -9382,10 +9386,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9408,13 +9412,13 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9465,7 +9469,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9474,7 +9478,7 @@
         <v>83</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>105</v>
@@ -9495,10 +9499,10 @@
         <v>81</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>81</v>
@@ -9506,10 +9510,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9532,13 +9536,13 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9589,7 +9593,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9610,16 +9614,16 @@
         <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -758,7 +758,7 @@
     <t>The data type is CodeableConcept because clinicalStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFencounterProblemStatus</t>
+    <t>http://va.gov/fhir/ValueSet/encounterProblemStatus</t>
   </si>
   <si>
     <t>con-3
@@ -800,7 +800,7 @@
 The data type is CodeableConcept because verificationStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFencounterProblemVerificationStatus</t>
+    <t>http://va.gov/fhir/ValueSet/encounterProblemVerificationStatus</t>
   </si>
   <si>
     <t>con-3
@@ -1936,7 +1936,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.85546875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.12890625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -1954,7 +1954,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="100.7578125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="136.5078125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="68.20703125" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2533" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2533" uniqueCount="510">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -772,6 +772,9 @@
   </si>
   <si>
     <t>Outpat.VDiagnosis.Modifier,Outpat.WorkloadVDiagnosis.Modifier</t>
+  </si>
+  <si>
+    <t>Diagnosis.CodeTableDetail.Diagnosis.OriginalText</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -933,6 +936,9 @@
   </si>
   <si>
     <t>Outpat.VDiagnosis.ICDIEN,Outpat.WorkloadVDiagnosis.ICDIEN</t>
+  </si>
+  <si>
+    <t>Diagnosis.Diagnosis,Diagnosis.CodeTableDetail.Diagnosis.Code</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1244,6 +1250,9 @@
     <t>Outpat.VDiagnosis.VisitDateTime,Outpat.VDiagnosis.VisitIEN,Outpat.WorkloadVDiagnosis.VisitDateTime,Outpat.WorkloadVDiagnosis.VisitIEN</t>
   </si>
   <si>
+    <t>Diagnosis.EncounterNumber,Diagnosis.EnteredAt,Diagnosis.EnteredBy,Diagnosis.EnteredOn,Diagnosis.FromTime,Diagnosis.ToTime</t>
+  </si>
+  <si>
     <t>Event.context</t>
   </si>
   <si>
@@ -1304,6 +1313,9 @@
     <t>Outpat.VDiagnosis.InjuryDateTime,Outpat.WorkloadVDiagnosis.InjuryDateTime</t>
   </si>
   <si>
+    <t>Diagnosis.OnsetTime</t>
+  </si>
+  <si>
     <t>Condition.abatement[x]</t>
   </si>
   <si>
@@ -1351,7 +1363,8 @@
 Immun.ImmunizationContraRefusalEvent.VisitDateTime,Outpat.Visit.VisitDateTime,Outpat.VisitLogic.VisitDateTime,Outpat.Workload.VisitDateTime</t>
   </si>
   <si>
-    <t>visit.dateTime,visit.visitString</t>
+    <t>Diagnosis.EncounterNumber,Diagnosis.EnteredAt,Diagnosis.EnteredBy,Diagnosis.EnteredOn,Diagnosis.FromTime,Diagnosis.ToTime
+Encounter.CareProvider.Description,Encounter.CareProvider.Name</t>
   </si>
   <si>
     <t>REL-11</t>
@@ -1380,6 +1393,9 @@
   </si>
   <si>
     <t>Outpat.VDiagnosis.EncounterProviderIEN,Outpat.WorkloadVDiagnosis.EncounterProviderIEN</t>
+  </si>
+  <si>
+    <t>Diagnosis.DiagnosingClinician</t>
   </si>
   <si>
     <t>.participation[typeCode=AUT].role</t>
@@ -1954,7 +1970,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="100.7578125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="136.5078125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="122.265625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="68.20703125" customWidth="true" bestFit="true"/>
@@ -4659,22 +4675,22 @@
         <v>243</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>82</v>
+        <v>244</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AS21" t="s" s="2">
         <v>82</v>
@@ -4682,10 +4698,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4711,13 +4727,13 @@
         <v>191</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4747,7 +4763,7 @@
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
@@ -4765,7 +4781,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>83</v>
@@ -4774,45 +4790,45 @@
         <v>94</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>243</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>82</v>
+        <v>244</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AS22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4838,13 +4854,13 @@
         <v>191</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4873,16 +4889,16 @@
         <v>196</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -4892,7 +4908,7 @@
         <v>143</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>83</v>
@@ -4919,16 +4935,16 @@
         <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AS23" t="s" s="2">
         <v>82</v>
@@ -4936,13 +4952,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>82</v>
@@ -4967,13 +4983,13 @@
         <v>191</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4984,7 +5000,7 @@
         <v>82</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>82</v>
@@ -5002,10 +5018,10 @@
         <v>196</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5023,7 +5039,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>83</v>
@@ -5038,7 +5054,7 @@
         <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
@@ -5050,16 +5066,16 @@
         <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AS24" t="s" s="2">
         <v>82</v>
@@ -5067,10 +5083,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5096,13 +5112,13 @@
         <v>191</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5131,10 +5147,10 @@
         <v>118</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5152,7 +5168,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>83</v>
@@ -5179,31 +5195,31 @@
         <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AS25" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5225,14 +5241,14 @@
         <v>191</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5260,10 +5276,10 @@
         <v>196</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -5281,7 +5297,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>83</v>
@@ -5296,39 +5312,39 @@
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>82</v>
+        <v>295</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AS26" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5452,10 +5468,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5581,10 +5597,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5607,19 +5623,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5668,7 +5684,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>83</v>
@@ -5698,10 +5714,10 @@
         <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>82</v>
@@ -5712,10 +5728,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5839,10 +5855,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5968,10 +5984,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5997,16 +6013,16 @@
         <v>108</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -6016,7 +6032,7 @@
         <v>82</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>82</v>
@@ -6055,7 +6071,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
@@ -6070,7 +6086,7 @@
         <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>82</v>
@@ -6085,10 +6101,10 @@
         <v>82</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>82</v>
@@ -6099,10 +6115,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6128,13 +6144,13 @@
         <v>170</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6184,7 +6200,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -6214,10 +6230,10 @@
         <v>82</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>82</v>
@@ -6228,10 +6244,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6257,14 +6273,14 @@
         <v>114</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6313,7 +6329,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -6328,13 +6344,13 @@
         <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>82</v>
+        <v>295</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>82</v>
@@ -6343,10 +6359,10 @@
         <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>82</v>
@@ -6357,10 +6373,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6386,14 +6402,14 @@
         <v>170</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6442,7 +6458,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -6472,10 +6488,10 @@
         <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>82</v>
@@ -6486,10 +6502,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6512,19 +6528,19 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6573,7 +6589,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
@@ -6603,10 +6619,10 @@
         <v>82</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>82</v>
@@ -6617,10 +6633,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6646,16 +6662,16 @@
         <v>170</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6704,7 +6720,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -6734,10 +6750,10 @@
         <v>82</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>82</v>
@@ -6748,10 +6764,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6777,13 +6793,13 @@
         <v>191</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6809,13 +6825,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6833,7 +6849,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -6860,31 +6876,31 @@
         <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AS38" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6903,17 +6919,17 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6962,7 +6978,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>94</v>
@@ -6977,28 +6993,28 @@
         <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AS39" t="s" s="2">
         <v>82</v>
@@ -7006,10 +7022,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7032,16 +7048,16 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7091,7 +7107,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -7106,28 +7122,28 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>82</v>
+        <v>394</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AS40" t="s" s="2">
         <v>82</v>
@@ -7135,10 +7151,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7161,16 +7177,16 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7208,7 +7224,7 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
@@ -7218,7 +7234,7 @@
         <v>143</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -7242,19 +7258,19 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AS41" t="s" s="2">
         <v>82</v>
@@ -7262,13 +7278,13 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>82</v>
@@ -7290,16 +7306,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7349,7 +7365,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
@@ -7364,28 +7380,28 @@
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>82</v>
+        <v>414</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AS42" t="s" s="2">
         <v>82</v>
@@ -7393,10 +7409,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7419,16 +7435,16 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7466,7 +7482,7 @@
         <v>82</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
@@ -7476,7 +7492,7 @@
         <v>143</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -7485,7 +7501,7 @@
         <v>94</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>106</v>
@@ -7509,10 +7525,10 @@
         <v>82</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>82</v>
@@ -7520,13 +7536,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>82</v>
@@ -7548,16 +7564,16 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7607,7 +7623,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -7616,34 +7632,34 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ44" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AL44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ44" t="s" s="2">
-        <v>416</v>
-      </c>
       <c r="AR44" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AS44" t="s" s="2">
         <v>82</v>
@@ -7651,10 +7667,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7677,13 +7693,13 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7734,7 +7750,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -7749,13 +7765,13 @@
         <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -7764,13 +7780,13 @@
         <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="AS45" t="s" s="2">
         <v>82</v>
@@ -7778,10 +7794,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7804,13 +7820,13 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7861,7 +7877,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -7876,13 +7892,13 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
@@ -7894,10 +7910,10 @@
         <v>82</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="AS46" t="s" s="2">
         <v>82</v>
@@ -7905,10 +7921,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7931,13 +7947,13 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7988,7 +8004,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8018,13 +8034,13 @@
         <v>82</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="AS47" t="s" s="2">
         <v>82</v>
@@ -8032,10 +8048,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8058,13 +8074,13 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8115,7 +8131,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8127,7 +8143,7 @@
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -8148,7 +8164,7 @@
         <v>82</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>82</v>
@@ -8159,10 +8175,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8286,10 +8302,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8415,14 +8431,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8444,10 +8460,10 @@
         <v>139</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>157</v>
@@ -8502,7 +8518,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -8546,10 +8562,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8575,10 +8591,10 @@
         <v>191</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8605,13 +8621,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8629,7 +8645,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -8638,7 +8654,7 @@
         <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>106</v>
@@ -8656,13 +8672,13 @@
         <v>82</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>82</v>
@@ -8673,10 +8689,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8699,13 +8715,13 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8756,7 +8772,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -8765,7 +8781,7 @@
         <v>84</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>106</v>
@@ -8789,7 +8805,7 @@
         <v>82</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>82</v>
@@ -8800,10 +8816,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8829,10 +8845,10 @@
         <v>191</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8859,13 +8875,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8883,7 +8899,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -8916,7 +8932,7 @@
         <v>82</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>82</v>
@@ -8927,10 +8943,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8953,16 +8969,16 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9012,7 +9028,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9024,7 +9040,7 @@
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -9045,7 +9061,7 @@
         <v>82</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>82</v>
@@ -9056,10 +9072,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9183,10 +9199,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9312,14 +9328,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9341,10 +9357,10 @@
         <v>139</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>157</v>
@@ -9399,7 +9415,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -9443,10 +9459,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9472,10 +9488,10 @@
         <v>191</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9502,13 +9518,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9526,7 +9542,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -9535,7 +9551,7 @@
         <v>84</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9550,19 +9566,19 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="AS59" t="s" s="2">
         <v>82</v>
@@ -9570,10 +9586,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9596,13 +9612,13 @@
         <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9653,7 +9669,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -9662,7 +9678,7 @@
         <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9686,10 +9702,10 @@
         <v>82</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="AS60" t="s" s="2">
         <v>82</v>
@@ -9697,10 +9713,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9723,13 +9739,13 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9780,7 +9796,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -9804,16 +9820,16 @@
         <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -774,7 +774,7 @@
     <t>Outpat.VDiagnosis.Modifier,Outpat.WorkloadVDiagnosis.Modifier</t>
   </si>
   <si>
-    <t>Diagnosis.CodeTableDetail.Diagnosis.OriginalText</t>
+    <t>Diagnosis.Diagnosis[CodeTableDetail.Diagnosis].OriginalText</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -938,7 +938,7 @@
     <t>Outpat.VDiagnosis.ICDIEN,Outpat.WorkloadVDiagnosis.ICDIEN</t>
   </si>
   <si>
-    <t>Diagnosis.Diagnosis,Diagnosis.CodeTableDetail.Diagnosis.Code</t>
+    <t>Diagnosis.Diagnosis,Diagnosis.Diagnosis[CodeTableDetail.Diagnosis].Code</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1364,7 +1364,7 @@
   </si>
   <si>
     <t>Diagnosis.EncounterNumber,Diagnosis.EnteredAt,Diagnosis.EnteredBy,Diagnosis.EnteredOn,Diagnosis.FromTime,Diagnosis.ToTime
-Encounter.CareProvider.Description,Encounter.CareProvider.Name</t>
+Encounter.ConsultingClinician[CareProvider].Description,Encounter.ConsultingClinician[CareProvider].Name</t>
   </si>
   <si>
     <t>REL-11</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file V POV (9000010.07) to us-core-condition-encounter-diagnosis</t>
+    <t>This StructureDefinition contains the maps for VistA file V POV (9000010.07) to us-core-condition-encounter-diagnosis.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2533" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2533" uniqueCount="511">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -491,6 +491,9 @@
   <si>
     <t xml:space="preserve">ele-1
 </t>
+  </si>
+  <si>
+    <t>2043: target not supported</t>
   </si>
   <si>
     <t>Condition.modifierExtension</t>
@@ -3246,7 +3249,7 @@
         <v>145</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>82</v>
@@ -3275,14 +3278,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3304,16 +3307,16 @@
         <v>139</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>82</v>
@@ -3362,7 +3365,7 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>83</v>
@@ -3406,10 +3409,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3432,19 +3435,19 @@
         <v>95</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>82</v>
@@ -3493,7 +3496,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>83</v>
@@ -3517,7 +3520,7 @@
         <v>82</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3526,10 +3529,10 @@
         <v>82</v>
       </c>
       <c r="AQ12" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AR12" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AS12" t="s" s="2">
         <v>82</v>
@@ -3537,10 +3540,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3563,13 +3566,13 @@
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3620,7 +3623,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>83</v>
@@ -3653,7 +3656,7 @@
         <v>82</v>
       </c>
       <c r="AQ13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AR13" t="s" s="2">
         <v>82</v>
@@ -3664,14 +3667,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3693,13 +3696,13 @@
         <v>139</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3740,7 +3743,7 @@
         <v>142</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>82</v>
@@ -3749,7 +3752,7 @@
         <v>143</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>83</v>
@@ -3782,7 +3785,7 @@
         <v>82</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AR14" t="s" s="2">
         <v>82</v>
@@ -3793,10 +3796,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3822,16 +3825,16 @@
         <v>114</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -3856,13 +3859,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -3880,7 +3883,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>83</v>
@@ -3913,7 +3916,7 @@
         <v>137</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AR15" t="s" s="2">
         <v>82</v>
@@ -3924,10 +3927,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3950,19 +3953,19 @@
         <v>95</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -3987,13 +3990,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -4011,7 +4014,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>83</v>
@@ -4041,10 +4044,10 @@
         <v>82</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AR16" t="s" s="2">
         <v>82</v>
@@ -4055,10 +4058,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4084,16 +4087,16 @@
         <v>108</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
@@ -4103,10 +4106,10 @@
         <v>82</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>82</v>
@@ -4142,7 +4145,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>83</v>
@@ -4157,7 +4160,7 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>82</v>
@@ -4172,10 +4175,10 @@
         <v>82</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AR17" t="s" s="2">
         <v>82</v>
@@ -4186,10 +4189,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4212,16 +4215,16 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4235,7 +4238,7 @@
         <v>82</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>82</v>
@@ -4271,7 +4274,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>83</v>
@@ -4286,7 +4289,7 @@
         <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>82</v>
@@ -4301,10 +4304,10 @@
         <v>82</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AR18" t="s" s="2">
         <v>82</v>
@@ -4315,10 +4318,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4341,13 +4344,13 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4398,7 +4401,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>83</v>
@@ -4428,10 +4431,10 @@
         <v>82</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AR19" t="s" s="2">
         <v>82</v>
@@ -4442,10 +4445,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4468,16 +4471,16 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4527,7 +4530,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>83</v>
@@ -4557,10 +4560,10 @@
         <v>82</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AR20" t="s" s="2">
         <v>82</v>
@@ -4571,10 +4574,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4597,16 +4600,16 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4632,11 +4635,11 @@
         <v>82</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>82</v>
@@ -4654,7 +4657,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>83</v>
@@ -4663,34 +4666,34 @@
         <v>94</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AS21" t="s" s="2">
         <v>82</v>
@@ -4698,10 +4701,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4724,16 +4727,16 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4759,11 +4762,11 @@
         <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
@@ -4781,7 +4784,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>83</v>
@@ -4790,45 +4793,45 @@
         <v>94</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AS22" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4851,16 +4854,16 @@
         <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4886,19 +4889,19 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -4908,7 +4911,7 @@
         <v>143</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>83</v>
@@ -4935,16 +4938,16 @@
         <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AS23" t="s" s="2">
         <v>82</v>
@@ -4952,13 +4955,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>82</v>
@@ -4980,16 +4983,16 @@
         <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5000,7 +5003,7 @@
         <v>82</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>82</v>
@@ -5015,13 +5018,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5039,7 +5042,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>83</v>
@@ -5054,7 +5057,7 @@
         <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
@@ -5066,16 +5069,16 @@
         <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AS24" t="s" s="2">
         <v>82</v>
@@ -5083,10 +5086,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5109,16 +5112,16 @@
         <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5147,10 +5150,10 @@
         <v>118</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5168,7 +5171,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>83</v>
@@ -5195,31 +5198,31 @@
         <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AS25" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5238,17 +5241,17 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5273,13 +5276,13 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -5297,7 +5300,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>83</v>
@@ -5312,39 +5315,39 @@
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AS26" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5367,13 +5370,13 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5424,7 +5427,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>83</v>
@@ -5457,7 +5460,7 @@
         <v>82</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>82</v>
@@ -5468,14 +5471,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5497,13 +5500,13 @@
         <v>139</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5544,7 +5547,7 @@
         <v>142</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>82</v>
@@ -5553,7 +5556,7 @@
         <v>143</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -5586,7 +5589,7 @@
         <v>82</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>82</v>
@@ -5597,10 +5600,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5623,19 +5626,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5684,7 +5687,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>83</v>
@@ -5714,10 +5717,10 @@
         <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>82</v>
@@ -5728,10 +5731,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5754,13 +5757,13 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5811,7 +5814,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>83</v>
@@ -5844,7 +5847,7 @@
         <v>82</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>82</v>
@@ -5855,14 +5858,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5884,13 +5887,13 @@
         <v>139</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5931,7 +5934,7 @@
         <v>142</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
@@ -5940,7 +5943,7 @@
         <v>143</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
@@ -5973,7 +5976,7 @@
         <v>82</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>82</v>
@@ -5984,10 +5987,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6013,16 +6016,16 @@
         <v>108</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -6032,7 +6035,7 @@
         <v>82</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>82</v>
@@ -6071,7 +6074,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
@@ -6086,7 +6089,7 @@
         <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>82</v>
@@ -6101,10 +6104,10 @@
         <v>82</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>82</v>
@@ -6115,10 +6118,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6141,16 +6144,16 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6200,7 +6203,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -6230,10 +6233,10 @@
         <v>82</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>82</v>
@@ -6244,10 +6247,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6273,14 +6276,14 @@
         <v>114</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6329,7 +6332,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -6344,13 +6347,13 @@
         <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>82</v>
@@ -6359,10 +6362,10 @@
         <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>82</v>
@@ -6373,10 +6376,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6399,17 +6402,17 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6458,7 +6461,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -6488,10 +6491,10 @@
         <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>82</v>
@@ -6502,10 +6505,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6528,19 +6531,19 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6589,7 +6592,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
@@ -6619,10 +6622,10 @@
         <v>82</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>82</v>
@@ -6633,10 +6636,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6659,19 +6662,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6720,7 +6723,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -6750,10 +6753,10 @@
         <v>82</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>82</v>
@@ -6764,10 +6767,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6790,16 +6793,16 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6825,13 +6828,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6849,7 +6852,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -6876,31 +6879,31 @@
         <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AS38" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6919,17 +6922,17 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6978,7 +6981,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>94</v>
@@ -6993,28 +6996,28 @@
         <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AS39" t="s" s="2">
         <v>82</v>
@@ -7022,10 +7025,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7048,16 +7051,16 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7107,7 +7110,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -7122,28 +7125,28 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AS40" t="s" s="2">
         <v>82</v>
@@ -7151,10 +7154,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7177,16 +7180,16 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7224,7 +7227,7 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
@@ -7234,7 +7237,7 @@
         <v>143</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -7258,19 +7261,19 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AS41" t="s" s="2">
         <v>82</v>
@@ -7278,13 +7281,13 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>82</v>
@@ -7306,16 +7309,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7365,7 +7368,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
@@ -7380,28 +7383,28 @@
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AS42" t="s" s="2">
         <v>82</v>
@@ -7409,10 +7412,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7435,16 +7438,16 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7482,7 +7485,7 @@
         <v>82</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
@@ -7492,7 +7495,7 @@
         <v>143</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -7501,7 +7504,7 @@
         <v>94</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>106</v>
@@ -7525,10 +7528,10 @@
         <v>82</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>82</v>
@@ -7536,13 +7539,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>82</v>
@@ -7564,16 +7567,16 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7623,7 +7626,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -7632,13 +7635,13 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>82</v>
@@ -7656,10 +7659,10 @@
         <v>82</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AS44" t="s" s="2">
         <v>82</v>
@@ -7667,10 +7670,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7693,13 +7696,13 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7750,7 +7753,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -7765,13 +7768,13 @@
         <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -7780,13 +7783,13 @@
         <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AS45" t="s" s="2">
         <v>82</v>
@@ -7794,10 +7797,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7820,13 +7823,13 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7877,7 +7880,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -7892,13 +7895,13 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
@@ -7910,10 +7913,10 @@
         <v>82</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AS46" t="s" s="2">
         <v>82</v>
@@ -7921,10 +7924,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7947,13 +7950,13 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8004,7 +8007,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8034,13 +8037,13 @@
         <v>82</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AS47" t="s" s="2">
         <v>82</v>
@@ -8048,10 +8051,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8074,13 +8077,13 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8131,7 +8134,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8143,7 +8146,7 @@
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -8164,7 +8167,7 @@
         <v>82</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>82</v>
@@ -8175,10 +8178,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8201,13 +8204,13 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8258,7 +8261,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -8291,7 +8294,7 @@
         <v>82</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>82</v>
@@ -8302,14 +8305,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8331,13 +8334,13 @@
         <v>139</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8387,7 +8390,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8420,7 +8423,7 @@
         <v>82</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>82</v>
@@ -8431,14 +8434,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8460,16 +8463,16 @@
         <v>139</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8518,7 +8521,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -8562,10 +8565,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8588,13 +8591,13 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8621,13 +8624,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8645,7 +8648,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -8654,7 +8657,7 @@
         <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>106</v>
@@ -8672,13 +8675,13 @@
         <v>82</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>82</v>
@@ -8689,10 +8692,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8715,13 +8718,13 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8772,7 +8775,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -8781,7 +8784,7 @@
         <v>84</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>106</v>
@@ -8805,7 +8808,7 @@
         <v>82</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>82</v>
@@ -8816,10 +8819,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8842,13 +8845,13 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8875,13 +8878,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8899,7 +8902,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -8932,7 +8935,7 @@
         <v>82</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>82</v>
@@ -8943,10 +8946,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8969,16 +8972,16 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9028,7 +9031,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9040,7 +9043,7 @@
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -9061,7 +9064,7 @@
         <v>82</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>82</v>
@@ -9072,10 +9075,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9098,13 +9101,13 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9155,7 +9158,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9188,7 +9191,7 @@
         <v>82</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>82</v>
@@ -9199,14 +9202,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9228,13 +9231,13 @@
         <v>139</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9284,7 +9287,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9317,7 +9320,7 @@
         <v>82</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>82</v>
@@ -9328,14 +9331,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9357,16 +9360,16 @@
         <v>139</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9415,7 +9418,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -9459,10 +9462,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9485,13 +9488,13 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9518,13 +9521,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9542,7 +9545,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -9551,7 +9554,7 @@
         <v>84</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9566,19 +9569,19 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AS59" t="s" s="2">
         <v>82</v>
@@ -9586,10 +9589,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9612,13 +9615,13 @@
         <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9669,7 +9672,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -9678,7 +9681,7 @@
         <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9702,10 +9705,10 @@
         <v>82</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AS60" t="s" s="2">
         <v>82</v>
@@ -9713,10 +9716,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9739,13 +9742,13 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9796,7 +9799,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -9820,16 +9823,16 @@
         <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2533" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2533" uniqueCount="512">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -696,7 +696,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>346: source value from V POV - IEN (9000010.07-.001)</t>
+    <t>346: source value based on V POV - IEN (9000010.07-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -769,6 +769,10 @@
   <si>
     <t>con-3
 con-4con-5</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ced-27-350:If (9000010.07-.06) is Null then exclude value {null}</t>
   </si>
   <si>
     <t>604: terminologyMaps using VF_encounterProblemStatus on V POV - MODIFIER (9000010.07-.06)</t>
@@ -935,7 +939,7 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-condition-code</t>
   </si>
   <si>
-    <t>1613: source value from V POV - POV &gt; ICD DIAGNOSIS (9000010.07-.01 &gt; 80-)</t>
+    <t>1613: source value based on V POV - POV &gt; ICD DIAGNOSIS (9000010.07-.01 &gt; 80-)</t>
   </si>
   <si>
     <t>Outpat.VDiagnosis.ICDIEN,Outpat.WorkloadVDiagnosis.ICDIEN</t>
@@ -1077,7 +1081,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1613-2: source value from V POV - POV &gt; ICD DIAGNOSIS - CODE NUMBER (9000010.07-.01 &gt; 80-.01)</t>
+    <t>1613-2: source value based on V POV - POV &gt; ICD DIAGNOSIS - CODE NUMBER (9000010.07-.01 &gt; 80-.01)</t>
   </si>
   <si>
     <t>Outpat.VDiagnosis.ICDIEN,Outpat.WorkloadVDiagnosis.ICDIEN
@@ -1213,7 +1217,7 @@
     <t>Group is typically used for veterinary or public health use cases.</t>
   </si>
   <si>
-    <t>1611: reference from V POV - PATIENT NAME (9000010.07-.02)</t>
+    <t>1611: reference based on V POV - PATIENT NAME (9000010.07-.02)</t>
   </si>
   <si>
     <t>Outpat.VDiagnosis.PatientIEN,Outpat.WorkloadVDiagnosis.PatientIEN</t>
@@ -1247,7 +1251,7 @@
     <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter. This record indicates the encounter this particular record is associated with.  In the case of a "new" diagnosis reflecting ongoing/revised information about the condition, this might be distinct from the first encounter in which the underlying condition was first "known".</t>
   </si>
   <si>
-    <t>368: source value from V POV - VISIT (9000010.07-.03)</t>
+    <t>368: source value based on V POV - VISIT (9000010.07-.03)</t>
   </si>
   <si>
     <t>Outpat.VDiagnosis.VisitDateTime,Outpat.VDiagnosis.VisitIEN,Outpat.WorkloadVDiagnosis.VisitDateTime,Outpat.WorkloadVDiagnosis.VisitIEN</t>
@@ -1310,7 +1314,7 @@
 </t>
   </si>
   <si>
-    <t>370: source value from V POV - DATE OF INJURY (9000010.07-.13)</t>
+    <t>370: source value based on V POV - DATE OF INJURY (9000010.07-.13)</t>
   </si>
   <si>
     <t>Outpat.VDiagnosis.InjuryDateTime,Outpat.WorkloadVDiagnosis.InjuryDateTime</t>
@@ -1359,7 +1363,7 @@
     <t>The recordedDate represents when this particular Condition record was created in the system, which is often a system-generated date.</t>
   </si>
   <si>
-    <t>372: source value from V POV - VISIT &gt; VISIT - VISIT/ADMIT DATE&amp;TIME (9000010.07-.03 &gt; 9000010-.01)</t>
+    <t>372: source value based on V POV - VISIT &gt; VISIT - VISIT/ADMIT DATE&amp;TIME (9000010.07-.03 &gt; 9000010-.01)</t>
   </si>
   <si>
     <t>Outpat.VDiagnosis.VisitDateTime,Outpat.VDiagnosis.VisitIEN,Outpat.WorkloadVDiagnosis.VisitDateTime,Outpat.WorkloadVDiagnosis.VisitIEN
@@ -1392,7 +1396,7 @@
     <t>Individual who recorded the record and takes responsibility for its content.</t>
   </si>
   <si>
-    <t>1833: reference from V POV - ENCOUNTER PROVIDER (9000010.07-1204)</t>
+    <t>1833: reference based on V POV - ENCOUNTER PROVIDER (9000010.07-1204)</t>
   </si>
   <si>
     <t>Outpat.VDiagnosis.EncounterProviderIEN,Outpat.WorkloadVDiagnosis.EncounterProviderIEN</t>
@@ -1971,7 +1975,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="100.7578125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="101.87890625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="136.5078125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="122.265625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
@@ -4669,31 +4673,31 @@
         <v>242</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>106</v>
+        <v>243</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AS21" t="s" s="2">
         <v>82</v>
@@ -4701,10 +4705,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4730,13 +4734,13 @@
         <v>192</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4766,7 +4770,7 @@
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
@@ -4784,7 +4788,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>83</v>
@@ -4793,45 +4797,45 @@
         <v>94</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AS22" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4857,13 +4861,13 @@
         <v>192</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4892,16 +4896,16 @@
         <v>197</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -4911,7 +4915,7 @@
         <v>143</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>83</v>
@@ -4938,16 +4942,16 @@
         <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AS23" t="s" s="2">
         <v>82</v>
@@ -4955,13 +4959,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>82</v>
@@ -4986,13 +4990,13 @@
         <v>192</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5003,7 +5007,7 @@
         <v>82</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>82</v>
@@ -5021,10 +5025,10 @@
         <v>197</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5042,7 +5046,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>83</v>
@@ -5057,7 +5061,7 @@
         <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
@@ -5069,16 +5073,16 @@
         <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AS24" t="s" s="2">
         <v>82</v>
@@ -5086,10 +5090,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5115,13 +5119,13 @@
         <v>192</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5150,10 +5154,10 @@
         <v>118</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5171,7 +5175,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>83</v>
@@ -5198,31 +5202,31 @@
         <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AS25" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5244,14 +5248,14 @@
         <v>192</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5279,10 +5283,10 @@
         <v>197</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -5300,7 +5304,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>83</v>
@@ -5315,39 +5319,39 @@
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AS26" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5471,10 +5475,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5600,10 +5604,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5626,19 +5630,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5687,7 +5691,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>83</v>
@@ -5717,10 +5721,10 @@
         <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>82</v>
@@ -5731,10 +5735,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5858,10 +5862,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5987,10 +5991,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6016,16 +6020,16 @@
         <v>108</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -6035,7 +6039,7 @@
         <v>82</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>82</v>
@@ -6074,7 +6078,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
@@ -6089,7 +6093,7 @@
         <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>82</v>
@@ -6104,10 +6108,10 @@
         <v>82</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>82</v>
@@ -6118,10 +6122,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6147,13 +6151,13 @@
         <v>171</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6203,7 +6207,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -6233,10 +6237,10 @@
         <v>82</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>82</v>
@@ -6247,10 +6251,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6276,14 +6280,14 @@
         <v>114</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6332,7 +6336,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -6347,13 +6351,13 @@
         <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>82</v>
@@ -6362,10 +6366,10 @@
         <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>82</v>
@@ -6376,10 +6380,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6405,14 +6409,14 @@
         <v>171</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6461,7 +6465,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -6491,10 +6495,10 @@
         <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>82</v>
@@ -6505,10 +6509,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6531,19 +6535,19 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6592,7 +6596,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
@@ -6622,10 +6626,10 @@
         <v>82</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>82</v>
@@ -6636,10 +6640,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6665,16 +6669,16 @@
         <v>171</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6723,7 +6727,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -6753,10 +6757,10 @@
         <v>82</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>82</v>
@@ -6767,10 +6771,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6796,13 +6800,13 @@
         <v>192</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6828,13 +6832,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6852,7 +6856,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -6879,31 +6883,31 @@
         <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AS38" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6922,17 +6926,17 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6981,7 +6985,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>94</v>
@@ -6996,28 +7000,28 @@
         <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AS39" t="s" s="2">
         <v>82</v>
@@ -7025,10 +7029,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7051,16 +7055,16 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7110,7 +7114,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -7125,28 +7129,28 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AS40" t="s" s="2">
         <v>82</v>
@@ -7154,10 +7158,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7180,16 +7184,16 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7227,7 +7231,7 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
@@ -7237,7 +7241,7 @@
         <v>143</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -7261,19 +7265,19 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AS41" t="s" s="2">
         <v>82</v>
@@ -7281,13 +7285,13 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>82</v>
@@ -7309,16 +7313,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7368,7 +7372,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
@@ -7383,28 +7387,28 @@
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AS42" t="s" s="2">
         <v>82</v>
@@ -7412,10 +7416,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7438,16 +7442,16 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7485,7 +7489,7 @@
         <v>82</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
@@ -7495,7 +7499,7 @@
         <v>143</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -7504,7 +7508,7 @@
         <v>94</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>106</v>
@@ -7528,10 +7532,10 @@
         <v>82</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>82</v>
@@ -7539,13 +7543,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>82</v>
@@ -7567,16 +7571,16 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7626,7 +7630,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -7635,13 +7639,13 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>82</v>
@@ -7659,10 +7663,10 @@
         <v>82</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AS44" t="s" s="2">
         <v>82</v>
@@ -7670,10 +7674,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7696,13 +7700,13 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7753,7 +7757,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -7768,13 +7772,13 @@
         <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -7783,13 +7787,13 @@
         <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AS45" t="s" s="2">
         <v>82</v>
@@ -7797,10 +7801,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7823,13 +7827,13 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7880,7 +7884,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -7895,13 +7899,13 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
@@ -7913,10 +7917,10 @@
         <v>82</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AS46" t="s" s="2">
         <v>82</v>
@@ -7924,10 +7928,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7950,13 +7954,13 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8007,7 +8011,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8037,13 +8041,13 @@
         <v>82</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AS47" t="s" s="2">
         <v>82</v>
@@ -8051,10 +8055,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8077,13 +8081,13 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8134,7 +8138,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8146,7 +8150,7 @@
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -8167,7 +8171,7 @@
         <v>82</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>82</v>
@@ -8178,10 +8182,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8305,10 +8309,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8434,14 +8438,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8463,10 +8467,10 @@
         <v>139</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>158</v>
@@ -8521,7 +8525,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -8565,10 +8569,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8594,10 +8598,10 @@
         <v>192</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8624,13 +8628,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8648,7 +8652,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -8657,7 +8661,7 @@
         <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>106</v>
@@ -8675,13 +8679,13 @@
         <v>82</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>82</v>
@@ -8692,10 +8696,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8718,13 +8722,13 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8775,7 +8779,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -8784,7 +8788,7 @@
         <v>84</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>106</v>
@@ -8808,7 +8812,7 @@
         <v>82</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>82</v>
@@ -8819,10 +8823,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8848,10 +8852,10 @@
         <v>192</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8878,13 +8882,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8902,7 +8906,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -8935,7 +8939,7 @@
         <v>82</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>82</v>
@@ -8946,10 +8950,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8972,16 +8976,16 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9031,7 +9035,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9043,7 +9047,7 @@
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -9064,7 +9068,7 @@
         <v>82</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>82</v>
@@ -9075,10 +9079,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9202,10 +9206,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9331,14 +9335,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9360,10 +9364,10 @@
         <v>139</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>158</v>
@@ -9418,7 +9422,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -9462,10 +9466,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9491,10 +9495,10 @@
         <v>192</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9521,13 +9525,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9545,7 +9549,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -9554,7 +9558,7 @@
         <v>84</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9569,19 +9573,19 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AS59" t="s" s="2">
         <v>82</v>
@@ -9589,10 +9593,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9615,13 +9619,13 @@
         <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9672,7 +9676,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -9681,7 +9685,7 @@
         <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9705,10 +9709,10 @@
         <v>82</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AS60" t="s" s="2">
         <v>82</v>
@@ -9716,10 +9720,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9742,13 +9746,13 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9799,7 +9803,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -9823,16 +9827,16 @@
         <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2533" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2535" uniqueCount="514">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -764,6 +764,9 @@
     <t>The data type is CodeableConcept because clinicalStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
+    <t>see mapping [VF_encounterProblemStatus](ConceptMap-VF-encounterProblemStatus.html)</t>
+  </si>
+  <si>
     <t>http://va.gov/fhir/ValueSet/encounterProblemStatus</t>
   </si>
   <si>
@@ -811,6 +814,9 @@
   <si>
     <t>verificationStatus is not required.  For example, when a patient has abdominal pain in the ED, there is not likely going to be a verification status.
 The data type is CodeableConcept because verificationStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
+  </si>
+  <si>
+    <t>see mapping [VF_encounterProblemVerificationStatus](ConceptMap-VF-encounterProblemVerificationStatus.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/encounterProblemVerificationStatus</t>
@@ -1964,7 +1970,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="105.81640625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="59.12890625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -4641,9 +4647,11 @@
       <c r="X21" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="Y21" s="2"/>
+      <c r="Y21" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="Z21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>82</v>
@@ -4670,34 +4678,34 @@
         <v>94</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AS21" t="s" s="2">
         <v>82</v>
@@ -4705,10 +4713,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4734,13 +4742,13 @@
         <v>192</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4768,9 +4776,11 @@
       <c r="X22" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="Y22" s="2"/>
+      <c r="Y22" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
@@ -4788,7 +4798,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>83</v>
@@ -4797,45 +4807,45 @@
         <v>94</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AS22" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4861,13 +4871,13 @@
         <v>192</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4896,16 +4906,16 @@
         <v>197</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -4915,7 +4925,7 @@
         <v>143</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>83</v>
@@ -4942,16 +4952,16 @@
         <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AS23" t="s" s="2">
         <v>82</v>
@@ -4959,13 +4969,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>82</v>
@@ -4990,13 +5000,13 @@
         <v>192</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5007,7 +5017,7 @@
         <v>82</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>82</v>
@@ -5025,28 +5035,28 @@
         <v>197</v>
       </c>
       <c r="Y24" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>83</v>
@@ -5061,7 +5071,7 @@
         <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
@@ -5073,16 +5083,16 @@
         <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AS24" t="s" s="2">
         <v>82</v>
@@ -5090,10 +5100,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5119,13 +5129,13 @@
         <v>192</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5154,28 +5164,28 @@
         <v>118</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>83</v>
@@ -5202,31 +5212,31 @@
         <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AS25" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5248,14 +5258,14 @@
         <v>192</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5283,10 +5293,10 @@
         <v>197</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -5304,7 +5314,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>83</v>
@@ -5319,39 +5329,39 @@
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AS26" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5475,10 +5485,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5604,10 +5614,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5630,19 +5640,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5691,7 +5701,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>83</v>
@@ -5721,10 +5731,10 @@
         <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>82</v>
@@ -5735,10 +5745,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5862,10 +5872,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5991,10 +6001,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6020,16 +6030,16 @@
         <v>108</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -6039,7 +6049,7 @@
         <v>82</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>82</v>
@@ -6078,7 +6088,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
@@ -6093,7 +6103,7 @@
         <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>82</v>
@@ -6108,10 +6118,10 @@
         <v>82</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>82</v>
@@ -6122,10 +6132,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6151,13 +6161,13 @@
         <v>171</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6207,7 +6217,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -6237,10 +6247,10 @@
         <v>82</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>82</v>
@@ -6251,10 +6261,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6280,14 +6290,14 @@
         <v>114</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6336,7 +6346,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -6351,13 +6361,13 @@
         <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>82</v>
@@ -6366,10 +6376,10 @@
         <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>82</v>
@@ -6380,10 +6390,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6409,14 +6419,14 @@
         <v>171</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6465,7 +6475,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -6495,10 +6505,10 @@
         <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>82</v>
@@ -6509,10 +6519,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6535,19 +6545,19 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6596,7 +6606,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
@@ -6626,10 +6636,10 @@
         <v>82</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>82</v>
@@ -6640,10 +6650,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6669,16 +6679,16 @@
         <v>171</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6727,7 +6737,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -6757,10 +6767,10 @@
         <v>82</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>82</v>
@@ -6771,10 +6781,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6800,13 +6810,13 @@
         <v>192</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6832,13 +6842,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6856,7 +6866,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -6883,31 +6893,31 @@
         <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AS38" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6926,17 +6936,17 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6985,7 +6995,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>94</v>
@@ -7000,28 +7010,28 @@
         <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AS39" t="s" s="2">
         <v>82</v>
@@ -7029,10 +7039,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7055,16 +7065,16 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7114,7 +7124,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -7129,28 +7139,28 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AS40" t="s" s="2">
         <v>82</v>
@@ -7158,10 +7168,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7184,16 +7194,16 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7231,7 +7241,7 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
@@ -7241,7 +7251,7 @@
         <v>143</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -7265,19 +7275,19 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AS41" t="s" s="2">
         <v>82</v>
@@ -7285,13 +7295,13 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>82</v>
@@ -7313,16 +7323,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7372,7 +7382,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
@@ -7387,28 +7397,28 @@
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AS42" t="s" s="2">
         <v>82</v>
@@ -7416,10 +7426,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7442,16 +7452,16 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7489,7 +7499,7 @@
         <v>82</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
@@ -7499,7 +7509,7 @@
         <v>143</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -7508,7 +7518,7 @@
         <v>94</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>106</v>
@@ -7532,10 +7542,10 @@
         <v>82</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>82</v>
@@ -7543,13 +7553,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>82</v>
@@ -7571,16 +7581,16 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7630,7 +7640,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -7639,13 +7649,13 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>82</v>
@@ -7663,10 +7673,10 @@
         <v>82</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AS44" t="s" s="2">
         <v>82</v>
@@ -7674,10 +7684,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7700,13 +7710,13 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7757,7 +7767,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -7772,13 +7782,13 @@
         <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -7787,13 +7797,13 @@
         <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AS45" t="s" s="2">
         <v>82</v>
@@ -7801,10 +7811,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7827,13 +7837,13 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7884,7 +7894,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -7899,13 +7909,13 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
@@ -7917,10 +7927,10 @@
         <v>82</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AS46" t="s" s="2">
         <v>82</v>
@@ -7928,10 +7938,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7954,13 +7964,13 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8011,7 +8021,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8041,13 +8051,13 @@
         <v>82</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AS47" t="s" s="2">
         <v>82</v>
@@ -8055,10 +8065,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8081,13 +8091,13 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8138,7 +8148,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8150,7 +8160,7 @@
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -8171,7 +8181,7 @@
         <v>82</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>82</v>
@@ -8182,10 +8192,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8309,10 +8319,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8438,14 +8448,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8467,10 +8477,10 @@
         <v>139</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>158</v>
@@ -8525,7 +8535,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -8569,10 +8579,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8598,10 +8608,10 @@
         <v>192</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8628,13 +8638,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8652,7 +8662,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -8661,7 +8671,7 @@
         <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>106</v>
@@ -8679,13 +8689,13 @@
         <v>82</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>82</v>
@@ -8696,10 +8706,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8722,13 +8732,13 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8779,7 +8789,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -8788,7 +8798,7 @@
         <v>84</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>106</v>
@@ -8812,7 +8822,7 @@
         <v>82</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>82</v>
@@ -8823,10 +8833,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8852,10 +8862,10 @@
         <v>192</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8882,13 +8892,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8906,7 +8916,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -8939,7 +8949,7 @@
         <v>82</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>82</v>
@@ -8950,10 +8960,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8976,16 +8986,16 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9035,7 +9045,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9047,7 +9057,7 @@
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -9068,7 +9078,7 @@
         <v>82</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>82</v>
@@ -9079,10 +9089,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9206,10 +9216,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9335,14 +9345,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9364,10 +9374,10 @@
         <v>139</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>158</v>
@@ -9422,7 +9432,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -9466,10 +9476,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9495,10 +9505,10 @@
         <v>192</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9525,13 +9535,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9549,7 +9559,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -9558,7 +9568,7 @@
         <v>84</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9573,19 +9583,19 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AS59" t="s" s="2">
         <v>82</v>
@@ -9593,10 +9603,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9619,13 +9629,13 @@
         <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9676,7 +9686,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -9685,7 +9695,7 @@
         <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9709,10 +9719,10 @@
         <v>82</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AS60" t="s" s="2">
         <v>82</v>
@@ -9720,10 +9730,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9746,13 +9756,13 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9803,7 +9813,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -9827,16 +9837,16 @@
         <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -775,7 +775,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ced-27-350:If (9000010.07-.06) is Null then exclude value {null}</t>
+ced-27-350:If (9000010.07-.06) is Null then exclude value {true}</t>
   </si>
   <si>
     <t>604: terminologyMaps using VF_encounterProblemStatus on V POV - MODIFIER (9000010.07-.06)</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$65</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2535" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2696" uniqueCount="529">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -493,6 +493,80 @@
 </t>
   </si>
   <si>
+    <t>Condition.extension:assertedDate.id</t>
+  </si>
+  <si>
+    <t>Condition.extension.id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Condition.extension:assertedDate.extension</t>
+  </si>
+  <si>
+    <t>Condition.extension.extension</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Condition.extension:assertedDate.url</t>
+  </si>
+  <si>
+    <t>Condition.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/condition-assertedDate</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Condition.extension:assertedDate.value[x]</t>
+  </si>
+  <si>
+    <t>Condition.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ext-1
+</t>
+  </si>
+  <si>
     <t>2043: target not supported</t>
   </si>
   <si>
@@ -554,18 +628,6 @@
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Condition.identifier.extension</t>
   </si>
   <si>
@@ -573,12 +635,6 @@
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Condition.identifier.use</t>
@@ -943,15 +999,6 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-condition-code</t>
-  </si>
-  <si>
-    <t>1613: source value based on V POV - POV &gt; ICD DIAGNOSIS (9000010.07-.01 &gt; 80-)</t>
-  </si>
-  <si>
-    <t>Outpat.VDiagnosis.ICDIEN,Outpat.WorkloadVDiagnosis.ICDIEN</t>
-  </si>
-  <si>
-    <t>Diagnosis.Diagnosis,Diagnosis.Diagnosis[CodeTableDetail.Diagnosis].Code</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1087,13 +1134,16 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1613-2: source value based on V POV - POV &gt; ICD DIAGNOSIS - CODE NUMBER (9000010.07-.01 &gt; 80-.01)</t>
+    <t>1613: source value based on V POV - POV &gt; ICD DIAGNOSIS - CODE NUMBER (9000010.07-.01 &gt; 80-.01)</t>
   </si>
   <si>
     <t>Outpat.VDiagnosis.ICDIEN,Outpat.WorkloadVDiagnosis.ICDIEN
 Dim.ICD10.ICD10Code,Dim.ICD9.ICD9Code</t>
   </si>
   <si>
+    <t>Diagnosis.Diagnosis,Diagnosis.Diagnosis[CodeTableDetail.Diagnosis].Code</t>
+  </si>
+  <si>
     <t>C*E.1</t>
   </si>
   <si>
@@ -1314,10 +1364,6 @@
   </si>
   <si>
     <t>onsetDateTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
   </si>
   <si>
     <t>370: source value based on V POV - DATE OF INJURY (9000010.07-.13)</t>
@@ -1943,7 +1989,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS61"/>
+  <dimension ref="A1:AS65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.5390625" customWidth="true" bestFit="true"/>
@@ -3259,7 +3305,7 @@
         <v>145</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>82</v>
@@ -3288,46 +3334,42 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>154</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="M11" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>159</v>
-      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>82</v>
       </c>
@@ -3375,19 +3417,19 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>82</v>
@@ -3408,7 +3450,7 @@
         <v>82</v>
       </c>
       <c r="AQ11" t="s" s="2">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="AR11" t="s" s="2">
         <v>82</v>
@@ -3419,10 +3461,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3433,7 +3475,7 @@
         <v>83</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>82</v>
@@ -3442,23 +3484,19 @@
         <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>82</v>
       </c>
@@ -3494,19 +3532,19 @@
         <v>82</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>83</v>
@@ -3518,7 +3556,7 @@
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>82</v>
@@ -3530,7 +3568,7 @@
         <v>82</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3539,10 +3577,10 @@
         <v>82</v>
       </c>
       <c r="AQ12" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AR12" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AS12" t="s" s="2">
         <v>82</v>
@@ -3550,10 +3588,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3561,7 +3599,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>94</v>
@@ -3576,22 +3614,24 @@
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>171</v>
+        <v>108</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>82</v>
@@ -3633,10 +3673,10 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>94</v>
@@ -3666,7 +3706,7 @@
         <v>82</v>
       </c>
       <c r="AQ13" t="s" s="2">
-        <v>175</v>
+        <v>137</v>
       </c>
       <c r="AR13" t="s" s="2">
         <v>82</v>
@@ -3677,21 +3717,21 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>82</v>
@@ -3703,17 +3743,15 @@
         <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -3750,34 +3788,34 @@
         <v>82</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>82</v>
@@ -3795,7 +3833,7 @@
         <v>82</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>175</v>
+        <v>137</v>
       </c>
       <c r="AR14" t="s" s="2">
         <v>82</v>
@@ -3806,21 +3844,21 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>82</v>
@@ -3829,22 +3867,22 @@
         <v>95</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -3869,13 +3907,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -3893,19 +3931,19 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -3923,10 +3961,10 @@
         <v>82</v>
       </c>
       <c r="AP15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ15" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AQ15" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="AR15" t="s" s="2">
         <v>82</v>
@@ -3937,10 +3975,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3951,7 +3989,7 @@
         <v>83</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>82</v>
@@ -3963,19 +4001,19 @@
         <v>95</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -4000,13 +4038,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -4024,13 +4062,13 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>82</v>
@@ -4048,19 +4086,19 @@
         <v>82</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>82</v>
+        <v>191</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AR16" t="s" s="2">
-        <v>82</v>
+        <v>193</v>
       </c>
       <c r="AS16" t="s" s="2">
         <v>82</v>
@@ -4068,10 +4106,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4085,29 +4123,25 @@
         <v>94</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>108</v>
+        <v>195</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>203</v>
+        <v>155</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
@@ -4116,10 +4150,10 @@
         <v>82</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>82</v>
@@ -4155,7 +4189,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>209</v>
+        <v>157</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>83</v>
@@ -4167,10 +4201,10 @@
         <v>82</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>210</v>
+        <v>82</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>82</v>
@@ -4185,10 +4219,10 @@
         <v>82</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>211</v>
+        <v>82</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>212</v>
+        <v>158</v>
       </c>
       <c r="AR17" t="s" s="2">
         <v>82</v>
@@ -4199,42 +4233,42 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4248,7 +4282,7 @@
         <v>82</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>217</v>
+        <v>82</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>82</v>
@@ -4272,34 +4306,34 @@
         <v>82</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>218</v>
+        <v>162</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>219</v>
+        <v>82</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>82</v>
@@ -4314,10 +4348,10 @@
         <v>82</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>220</v>
+        <v>82</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>221</v>
+        <v>158</v>
       </c>
       <c r="AR18" t="s" s="2">
         <v>82</v>
@@ -4328,10 +4362,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4348,22 +4382,26 @@
         <v>82</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>223</v>
+        <v>114</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
       </c>
@@ -4387,13 +4425,13 @@
         <v>82</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>82</v>
+        <v>204</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>82</v>
@@ -4411,7 +4449,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>83</v>
@@ -4441,10 +4479,10 @@
         <v>82</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>227</v>
+        <v>137</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="AR19" t="s" s="2">
         <v>82</v>
@@ -4455,10 +4493,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4481,18 +4519,20 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
       </c>
@@ -4516,13 +4556,13 @@
         <v>82</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>82</v>
+        <v>216</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>82</v>
+        <v>217</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>82</v>
@@ -4540,7 +4580,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>83</v>
@@ -4570,10 +4610,10 @@
         <v>82</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>236</v>
+        <v>208</v>
       </c>
       <c r="AR20" t="s" s="2">
         <v>82</v>
@@ -4584,10 +4624,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4604,24 +4644,26 @@
         <v>95</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>192</v>
+        <v>108</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
       </c>
@@ -4630,10 +4672,10 @@
         <v>82</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="U21" t="s" s="2">
         <v>82</v>
@@ -4645,13 +4687,13 @@
         <v>82</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>241</v>
+        <v>82</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>82</v>
@@ -4669,7 +4711,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>83</v>
@@ -4678,34 +4720,34 @@
         <v>94</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>243</v>
+        <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>244</v>
+        <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>246</v>
+        <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>247</v>
+        <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>248</v>
+        <v>82</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>249</v>
+        <v>82</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>250</v>
+        <v>229</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>252</v>
+        <v>82</v>
       </c>
       <c r="AS21" t="s" s="2">
         <v>82</v>
@@ -4713,10 +4755,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4733,22 +4775,22 @@
         <v>95</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4762,7 +4804,7 @@
         <v>82</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>82</v>
+        <v>235</v>
       </c>
       <c r="U22" t="s" s="2">
         <v>82</v>
@@ -4774,13 +4816,13 @@
         <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>257</v>
+        <v>82</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>258</v>
+        <v>82</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
@@ -4798,7 +4840,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>83</v>
@@ -4807,45 +4849,45 @@
         <v>94</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>259</v>
+        <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>260</v>
+        <v>237</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>246</v>
+        <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>247</v>
+        <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>248</v>
+        <v>82</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>261</v>
+        <v>82</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>263</v>
+        <v>239</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>252</v>
+        <v>82</v>
       </c>
       <c r="AS22" t="s" s="2">
-        <v>264</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>265</v>
+        <v>240</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>265</v>
+        <v>240</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4853,32 +4895,30 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G23" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="G23" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J23" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K23" t="s" s="2">
-        <v>192</v>
+        <v>241</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4903,35 +4943,37 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>267</v>
+        <v>82</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AC23" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
@@ -4952,16 +4994,16 @@
         <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>272</v>
+        <v>245</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>273</v>
+        <v>246</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>274</v>
+        <v>82</v>
       </c>
       <c r="AS23" t="s" s="2">
         <v>82</v>
@@ -4969,44 +5011,42 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>275</v>
+        <v>247</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K24" t="s" s="2">
-        <v>192</v>
+        <v>248</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5017,7 +5057,7 @@
         <v>82</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>278</v>
+        <v>82</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>82</v>
@@ -5032,13 +5072,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>267</v>
+        <v>82</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5056,13 +5096,13 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
@@ -5071,7 +5111,7 @@
         <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>279</v>
+        <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
@@ -5083,16 +5123,16 @@
         <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>274</v>
+        <v>82</v>
       </c>
       <c r="AS24" t="s" s="2">
         <v>82</v>
@@ -5100,10 +5140,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5117,25 +5157,25 @@
         <v>94</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>281</v>
+        <v>256</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>282</v>
+        <v>257</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>283</v>
+        <v>258</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5161,13 +5201,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>118</v>
+        <v>204</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5185,7 +5225,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>83</v>
@@ -5194,53 +5234,53 @@
         <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>82</v>
+        <v>261</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>106</v>
+        <v>262</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>82</v>
+        <v>263</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>82</v>
+        <v>265</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>285</v>
+        <v>267</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="AS25" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>290</v>
+        <v>271</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>290</v>
+        <v>271</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>94</v>
@@ -5249,24 +5289,24 @@
         <v>95</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5290,13 +5330,13 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -5314,7 +5354,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>290</v>
+        <v>271</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>83</v>
@@ -5323,45 +5363,45 @@
         <v>94</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>82</v>
+        <v>277</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>297</v>
+        <v>278</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>298</v>
+        <v>264</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>299</v>
+        <v>265</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>300</v>
+        <v>266</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>303</v>
+        <v>281</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="AS26" t="s" s="2">
-        <v>305</v>
+        <v>282</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5369,13 +5409,13 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>82</v>
@@ -5384,15 +5424,17 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>172</v>
+        <v>284</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5417,43 +5459,41 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>82</v>
+        <v>285</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>82</v>
+        <v>287</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>174</v>
+        <v>283</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
@@ -5468,16 +5508,16 @@
         <v>82</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>175</v>
+        <v>291</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="AS27" t="s" s="2">
         <v>82</v>
@@ -5485,24 +5525,26 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="D28" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>82</v>
@@ -5511,16 +5553,16 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>139</v>
+        <v>210</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>177</v>
+        <v>295</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>178</v>
+        <v>285</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>158</v>
+        <v>286</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5531,7 +5573,7 @@
         <v>82</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>82</v>
+        <v>296</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>82</v>
@@ -5546,31 +5588,31 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>82</v>
+        <v>285</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>82</v>
+        <v>287</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>180</v>
+        <v>283</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -5582,10 +5624,10 @@
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>82</v>
+        <v>297</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>82</v>
@@ -5597,16 +5639,16 @@
         <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>175</v>
+        <v>291</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="AS28" t="s" s="2">
         <v>82</v>
@@ -5614,10 +5656,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5628,7 +5670,7 @@
         <v>83</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5637,23 +5679,21 @@
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>309</v>
+        <v>210</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5677,13 +5717,13 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -5701,13 +5741,13 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
@@ -5728,59 +5768,61 @@
         <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>82</v>
+        <v>303</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>82</v>
+        <v>306</v>
       </c>
       <c r="AS29" t="s" s="2">
-        <v>82</v>
+        <v>307</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>82</v>
+        <v>309</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>172</v>
+        <v>310</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>173</v>
+        <v>311</v>
       </c>
       <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+      <c r="O30" t="s" s="2">
+        <v>312</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5804,13 +5846,13 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
@@ -5828,7 +5870,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>174</v>
+        <v>308</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>83</v>
@@ -5840,7 +5882,7 @@
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
@@ -5852,41 +5894,41 @@
         <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>82</v>
+        <v>315</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>82</v>
+        <v>316</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>82</v>
+        <v>317</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>175</v>
+        <v>318</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>82</v>
+        <v>319</v>
       </c>
       <c r="AS30" t="s" s="2">
-        <v>82</v>
+        <v>320</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
@@ -5898,17 +5940,15 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>139</v>
+        <v>195</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5945,31 +5985,31 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -5990,7 +6030,7 @@
         <v>82</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>82</v>
@@ -6001,46 +6041,44 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>320</v>
+        <v>197</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>321</v>
+        <v>198</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -6049,7 +6087,7 @@
         <v>82</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>324</v>
+        <v>82</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>82</v>
@@ -6076,34 +6114,34 @@
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>325</v>
+        <v>162</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>82</v>
@@ -6118,10 +6156,10 @@
         <v>82</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>327</v>
+        <v>82</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>328</v>
+        <v>158</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>82</v>
@@ -6132,10 +6170,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6146,7 +6184,7 @@
         <v>83</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -6158,18 +6196,20 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>171</v>
+        <v>324</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -6217,13 +6257,13 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
@@ -6247,10 +6287,10 @@
         <v>82</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>82</v>
@@ -6261,10 +6301,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6278,27 +6318,25 @@
         <v>94</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>114</v>
+        <v>195</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>337</v>
+        <v>155</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>338</v>
+        <v>156</v>
       </c>
       <c r="N34" s="2"/>
-      <c r="O34" t="s" s="2">
-        <v>339</v>
-      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -6346,7 +6384,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>340</v>
+        <v>157</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -6358,16 +6396,16 @@
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>341</v>
+        <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>82</v>
@@ -6376,10 +6414,10 @@
         <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>343</v>
+        <v>82</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>344</v>
+        <v>158</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>82</v>
@@ -6390,21 +6428,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -6413,21 +6451,21 @@
         <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>346</v>
+        <v>197</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6463,31 +6501,31 @@
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>349</v>
+        <v>162</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
@@ -6505,10 +6543,10 @@
         <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>351</v>
+        <v>158</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>82</v>
@@ -6519,10 +6557,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6536,7 +6574,7 @@
         <v>94</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>82</v>
@@ -6545,19 +6583,19 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>353</v>
+        <v>108</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>354</v>
+        <v>335</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>356</v>
+        <v>337</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>357</v>
+        <v>338</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6567,7 +6605,7 @@
         <v>82</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>82</v>
+        <v>339</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>82</v>
@@ -6606,7 +6644,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
@@ -6621,7 +6659,7 @@
         <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>82</v>
+        <v>341</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>82</v>
@@ -6636,10 +6674,10 @@
         <v>82</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>82</v>
@@ -6650,10 +6688,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6676,20 +6714,18 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>365</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6737,7 +6773,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -6767,10 +6803,10 @@
         <v>82</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>82</v>
@@ -6781,10 +6817,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6795,10 +6831,10 @@
         <v>83</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>82</v>
@@ -6807,18 +6843,18 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>192</v>
+        <v>114</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6842,13 +6878,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>373</v>
+        <v>82</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>374</v>
+        <v>82</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6866,13 +6902,13 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
@@ -6881,53 +6917,53 @@
         <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>82</v>
+        <v>356</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>376</v>
+        <v>82</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>82</v>
+        <v>359</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AS38" t="s" s="2">
-        <v>378</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>380</v>
+        <v>82</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
@@ -6936,17 +6972,17 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>381</v>
+        <v>195</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>382</v>
+        <v>362</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>383</v>
+        <v>363</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6995,10 +7031,10 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>94</v>
@@ -7010,28 +7046,28 @@
         <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>386</v>
+        <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>388</v>
+        <v>366</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>389</v>
+        <v>367</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>390</v>
+        <v>82</v>
       </c>
       <c r="AS39" t="s" s="2">
         <v>82</v>
@@ -7039,10 +7075,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7056,7 +7092,7 @@
         <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>82</v>
@@ -7065,18 +7101,20 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>393</v>
+        <v>370</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -7124,7 +7162,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -7139,28 +7177,28 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>396</v>
+        <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>398</v>
+        <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>399</v>
+        <v>82</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>401</v>
+        <v>376</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>402</v>
+        <v>82</v>
       </c>
       <c r="AS40" t="s" s="2">
         <v>82</v>
@@ -7168,10 +7206,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>403</v>
+        <v>377</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>403</v>
+        <v>377</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7185,7 +7223,7 @@
         <v>94</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>82</v>
@@ -7194,18 +7232,20 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>404</v>
+        <v>195</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>405</v>
+        <v>378</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>406</v>
+        <v>379</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7241,17 +7281,19 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AC41" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>403</v>
+        <v>382</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -7275,19 +7317,19 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>409</v>
+        <v>82</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>410</v>
+        <v>383</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>411</v>
+        <v>384</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="AS41" t="s" s="2">
         <v>82</v>
@@ -7295,14 +7337,12 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>413</v>
+        <v>385</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>414</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7311,10 +7351,10 @@
         <v>83</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>82</v>
@@ -7323,16 +7363,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>415</v>
+        <v>210</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>405</v>
+        <v>386</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>406</v>
+        <v>387</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>407</v>
+        <v>388</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7358,13 +7398,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>82</v>
+        <v>389</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>82</v>
+        <v>390</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>82</v>
+        <v>391</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7382,13 +7422,13 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>403</v>
+        <v>385</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
@@ -7397,47 +7437,47 @@
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>416</v>
+        <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>417</v>
+        <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>409</v>
+        <v>82</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>82</v>
+        <v>392</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="AS42" t="s" s="2">
-        <v>82</v>
+        <v>394</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>419</v>
+        <v>395</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>419</v>
+        <v>395</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>82</v>
+        <v>396</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>94</v>
@@ -7449,21 +7489,21 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>420</v>
+        <v>398</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7499,53 +7539,55 @@
         <v>82</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AC43" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>419</v>
+        <v>395</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>423</v>
+        <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>82</v>
+        <v>401</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>82</v>
+        <v>402</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>82</v>
+        <v>403</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>82</v>
+        <v>404</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>424</v>
+        <v>405</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>425</v>
+        <v>406</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>82</v>
@@ -7553,14 +7595,12 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>426</v>
+        <v>407</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>427</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7578,19 +7618,19 @@
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7640,7 +7680,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -7649,34 +7689,34 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>423</v>
+        <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>82</v>
+        <v>414</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>82</v>
+        <v>415</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>82</v>
+        <v>416</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="AS44" t="s" s="2">
         <v>82</v>
@@ -7684,10 +7724,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7710,15 +7750,17 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>422</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>423</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7755,19 +7797,17 @@
         <v>82</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="AC45" s="2"/>
       <c r="AD45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -7782,28 +7822,28 @@
         <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>432</v>
+        <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>433</v>
+        <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>82</v>
+        <v>425</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="AS45" t="s" s="2">
         <v>82</v>
@@ -7811,12 +7851,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C46" s="2"/>
+        <v>419</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="D46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7837,15 +7879,17 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>439</v>
+        <v>172</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>440</v>
+        <v>421</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>422</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>423</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7894,7 +7938,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>438</v>
+        <v>419</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -7909,28 +7953,28 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>82</v>
+        <v>425</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>82</v>
+        <v>426</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>446</v>
+        <v>428</v>
       </c>
       <c r="AS46" t="s" s="2">
         <v>82</v>
@@ -7938,10 +7982,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7955,24 +7999,26 @@
         <v>94</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>448</v>
+        <v>420</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -8009,19 +8055,17 @@
         <v>82</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8030,7 +8074,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>82</v>
+        <v>438</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -8051,13 +8095,13 @@
         <v>82</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>451</v>
+        <v>82</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="AS47" t="s" s="2">
         <v>82</v>
@@ -8065,12 +8109,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>442</v>
+      </c>
       <c r="D48" t="s" s="2">
         <v>82</v>
       </c>
@@ -8079,10 +8125,10 @@
         <v>83</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>82</v>
@@ -8091,15 +8137,17 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>455</v>
+        <v>172</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>456</v>
+        <v>435</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8148,22 +8196,22 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>82</v>
+        <v>438</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>458</v>
+        <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>82</v>
@@ -8181,10 +8229,10 @@
         <v>82</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>459</v>
+        <v>439</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="AS48" t="s" s="2">
         <v>82</v>
@@ -8192,10 +8240,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>460</v>
+        <v>444</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>460</v>
+        <v>444</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8209,22 +8257,22 @@
         <v>94</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>172</v>
+        <v>445</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>173</v>
+        <v>446</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8275,7 +8323,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>174</v>
+        <v>444</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -8287,16 +8335,16 @@
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>82</v>
+        <v>447</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>82</v>
+        <v>448</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>82</v>
@@ -8305,13 +8353,13 @@
         <v>82</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>82</v>
+        <v>450</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>175</v>
+        <v>451</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>82</v>
+        <v>452</v>
       </c>
       <c r="AS49" t="s" s="2">
         <v>82</v>
@@ -8319,43 +8367,41 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>139</v>
+        <v>454</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>177</v>
+        <v>455</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8404,28 +8450,28 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>180</v>
+        <v>453</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>82</v>
+        <v>457</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>82</v>
@@ -8437,10 +8483,10 @@
         <v>82</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>175</v>
+        <v>460</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>82</v>
+        <v>461</v>
       </c>
       <c r="AS50" t="s" s="2">
         <v>82</v>
@@ -8455,26 +8501,26 @@
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>463</v>
+        <v>82</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>139</v>
+        <v>463</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>464</v>
@@ -8482,12 +8528,8 @@
       <c r="M51" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="N51" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>159</v>
-      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8535,43 +8577,43 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AG51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AQ51" t="s" s="2">
-        <v>137</v>
+        <v>467</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>82</v>
+        <v>468</v>
       </c>
       <c r="AS51" t="s" s="2">
         <v>82</v>
@@ -8579,10 +8621,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8593,7 +8635,7 @@
         <v>83</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8605,13 +8647,13 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>192</v>
+        <v>470</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8638,13 +8680,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>373</v>
+        <v>82</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>470</v>
+        <v>82</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>471</v>
+        <v>82</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8662,19 +8704,19 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>472</v>
+        <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>106</v>
+        <v>473</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8689,13 +8731,13 @@
         <v>82</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>473</v>
+        <v>82</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>250</v>
+        <v>82</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>303</v>
+        <v>474</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>82</v>
@@ -8706,10 +8748,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8720,7 +8762,7 @@
         <v>83</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -8732,13 +8774,13 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>475</v>
+        <v>195</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>476</v>
+        <v>155</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>477</v>
+        <v>156</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8789,19 +8831,19 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>474</v>
+        <v>157</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>472</v>
+        <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
@@ -8822,7 +8864,7 @@
         <v>82</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>478</v>
+        <v>158</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>82</v>
@@ -8833,21 +8875,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8859,15 +8901,17 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>192</v>
+        <v>139</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>480</v>
+        <v>197</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8892,13 +8936,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>373</v>
+        <v>82</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>482</v>
+        <v>82</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>483</v>
+        <v>82</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8916,19 +8960,19 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>479</v>
+        <v>162</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -8949,7 +8993,7 @@
         <v>82</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>484</v>
+        <v>158</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>82</v>
@@ -8960,14 +9004,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>82</v>
+        <v>478</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8980,24 +9024,26 @@
         <v>82</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>455</v>
+        <v>139</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -9045,7 +9091,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9057,7 +9103,7 @@
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>489</v>
+        <v>145</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -9078,7 +9124,7 @@
         <v>82</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>490</v>
+        <v>137</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>82</v>
@@ -9089,10 +9135,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9115,13 +9161,13 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>172</v>
+        <v>483</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>173</v>
+        <v>484</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9148,13 +9194,13 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>82</v>
+        <v>389</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>82</v>
+        <v>485</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>82</v>
+        <v>486</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -9172,7 +9218,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>174</v>
+        <v>482</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9181,10 +9227,10 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>82</v>
+        <v>487</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -9199,13 +9245,13 @@
         <v>82</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>82</v>
+        <v>488</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>175</v>
+        <v>318</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>82</v>
@@ -9216,14 +9262,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9242,17 +9288,15 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>139</v>
+        <v>490</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>177</v>
+        <v>491</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>492</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9301,7 +9345,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>180</v>
+        <v>489</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9310,10 +9354,10 @@
         <v>84</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>82</v>
+        <v>487</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
@@ -9334,7 +9378,7 @@
         <v>82</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>175</v>
+        <v>493</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>82</v>
@@ -9345,46 +9389,42 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>463</v>
+        <v>82</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>139</v>
+        <v>210</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>464</v>
+        <v>495</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
       </c>
@@ -9408,13 +9448,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>82</v>
+        <v>389</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>82</v>
+        <v>497</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>82</v>
+        <v>498</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -9432,19 +9472,19 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>466</v>
+        <v>494</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
@@ -9465,7 +9505,7 @@
         <v>82</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>137</v>
+        <v>499</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>82</v>
@@ -9476,10 +9516,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9499,18 +9539,20 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>192</v>
+        <v>470</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>502</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>503</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9535,13 +9577,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>373</v>
+        <v>82</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>497</v>
+        <v>82</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>498</v>
+        <v>82</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9559,7 +9601,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -9568,10 +9610,10 @@
         <v>84</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>499</v>
+        <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>106</v>
+        <v>504</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
@@ -9583,19 +9625,19 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>500</v>
+        <v>82</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>502</v>
+        <v>82</v>
       </c>
       <c r="AS59" t="s" s="2">
         <v>82</v>
@@ -9603,10 +9645,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9617,7 +9659,7 @@
         <v>83</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9626,16 +9668,16 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>504</v>
+        <v>195</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>505</v>
+        <v>155</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>506</v>
+        <v>156</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9686,19 +9728,19 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>503</v>
+        <v>157</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>499</v>
+        <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -9719,10 +9761,10 @@
         <v>82</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>478</v>
+        <v>158</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>502</v>
+        <v>82</v>
       </c>
       <c r="AS60" t="s" s="2">
         <v>82</v>
@@ -9737,7 +9779,7 @@
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9756,15 +9798,17 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>508</v>
+        <v>139</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>509</v>
+        <v>197</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9813,7 +9857,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>507</v>
+        <v>162</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -9825,38 +9869,550 @@
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AR61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS61" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ62" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AR62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS62" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AK61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="AQ61" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="AR61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS61" t="s" s="2">
+      <c r="AK63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ63" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AR63" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AS63" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ64" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AR64" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AS64" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AQ65" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AR65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS65" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS61">
+  <autoFilter ref="A1:AS65">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9866,7 +10422,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI60">
+  <conditionalFormatting sqref="A2:AI64">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1273,7 +1273,7 @@
     <t>Group is typically used for veterinary or public health use cases.</t>
   </si>
   <si>
-    <t>1611: reference based on V POV - PATIENT NAME (9000010.07-.02)</t>
+    <t>1611: reference based on V POV - PATIENT NAME &gt; PATIENT/IHS - NAME (9000010.07-.02 &gt; 9000001-.01)</t>
   </si>
   <si>
     <t>Outpat.VDiagnosis.PatientIEN,Outpat.WorkloadVDiagnosis.PatientIEN</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
+++ b/docs/StructureDefinition-ConditionEncounterDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
